--- a/tools/comparison_outputs/EUA_1_Pro_radiation_comparison.xlsx
+++ b/tools/comparison_outputs/EUA_1_Pro_radiation_comparison.xlsx
@@ -195,7 +195,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>43092.36999999999</v>
+        <v>43214.48</v>
       </c>
     </row>
     <row r="16">
@@ -225,7 +225,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>70675934.42999995</v>
+        <v>70993337.53999995</v>
       </c>
     </row>
     <row r="19">
@@ -235,7 +235,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>70798951.47999996</v>
+        <v>70563308.60999995</v>
       </c>
     </row>
     <row r="20">
@@ -245,7 +245,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>-20.86721224667654</v>
+        <v>-20.511829708922452</v>
       </c>
     </row>
     <row r="21">
@@ -255,7 +255,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>-20.729475375049713</v>
+        <v>-20.99331450738921</v>
       </c>
     </row>
   </sheetData>
@@ -419,7 +419,7 @@
         <v>240.5197373075855</v>
       </c>
       <c r="E2">
-        <v>241.36</v>
+        <v>241.44</v>
       </c>
       <c r="F2">
         <v>236.51</v>
@@ -428,16 +428,16 @@
         <v>485944.63162500004</v>
       </c>
       <c r="H2">
-        <v>391366.02000000014</v>
+        <v>389125.70999999973</v>
       </c>
       <c r="I2">
-        <v>389212.18000000063</v>
+        <v>388756.7700000014</v>
       </c>
       <c r="J2">
-        <v>-0.199060644628434</v>
+        <v>-0.19999780900964412</v>
       </c>
       <c r="K2">
-        <v>-0.19462837012671338</v>
+        <v>-0.19923858671148933</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
         <v>0.9981022775173187</v>
       </c>
       <c r="X2">
-        <v>0.9981099628905308</v>
+        <v>0.9981102451547726</v>
       </c>
       <c r="Y2">
         <v>0.9976096153259277</v>
@@ -514,7 +514,7 @@
         <v>234.9731577045585</v>
       </c>
       <c r="E3">
-        <v>237.42</v>
+        <v>237.4</v>
       </c>
       <c r="F3">
         <v>226.27</v>
@@ -523,16 +523,16 @@
         <v>489043.429234375</v>
       </c>
       <c r="H3">
-        <v>388736.2000000003</v>
+        <v>387949.21000000037</v>
       </c>
       <c r="I3">
-        <v>373904.13999999955</v>
+        <v>374420.8399999996</v>
       </c>
       <c r="J3">
-        <v>-0.2354377594125587</v>
+        <v>-0.23438120703067927</v>
       </c>
       <c r="K3">
-        <v>-0.205109041933988</v>
+        <v>-0.20671828551636678</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         <v>0.9959379136562347</v>
       </c>
       <c r="X3">
-        <v>0.9959189402952531</v>
+        <v>0.9959185967381373</v>
       </c>
       <c r="Y3">
         <v>0.9951106905937195</v>
@@ -609,7 +609,7 @@
         <v>246.40961092436055</v>
       </c>
       <c r="E4">
-        <v>250.03</v>
+        <v>250.06</v>
       </c>
       <c r="F4">
         <v>233.35</v>
@@ -618,16 +618,16 @@
         <v>498712.398703125</v>
       </c>
       <c r="H4">
-        <v>367511.7599999998</v>
+        <v>360618.27000000107</v>
       </c>
       <c r="I4">
-        <v>336600.3399999993</v>
+        <v>346480.56000000006</v>
       </c>
       <c r="J4">
-        <v>-0.3250612158925454</v>
+        <v>-0.3052497573731789</v>
       </c>
       <c r="K4">
-        <v>-0.26307875850751955</v>
+        <v>-0.27690133444091297</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>0.9956513941287994</v>
       </c>
       <c r="X4">
-        <v>0.9956420552922723</v>
+        <v>0.9956425197421171</v>
       </c>
       <c r="Y4">
         <v>0.9936386942863464</v>
@@ -704,7 +704,7 @@
         <v>53.34289675933517</v>
       </c>
       <c r="E5">
-        <v>55.32</v>
+        <v>54.61</v>
       </c>
       <c r="F5">
         <v>50.64</v>
@@ -713,16 +713,16 @@
         <v>131528.94975</v>
       </c>
       <c r="H5">
-        <v>56974.609999999826</v>
+        <v>52679.16000000011</v>
       </c>
       <c r="I5">
-        <v>50375.15999999993</v>
+        <v>47341.57000000017</v>
       </c>
       <c r="J5">
-        <v>-0.6170032521680655</v>
+        <v>-0.6400673000888143</v>
       </c>
       <c r="K5">
-        <v>-0.5668283666197234</v>
+        <v>-0.5994861960037804</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>0.7078905999660492</v>
       </c>
       <c r="X5">
-        <v>0.7151827050824904</v>
+        <v>0.715941774048477</v>
       </c>
       <c r="Y5">
         <v>0.6290975213050842</v>
@@ -799,7 +799,7 @@
         <v>76.47038252428983</v>
       </c>
       <c r="E6">
-        <v>78.64</v>
+        <v>78.67</v>
       </c>
       <c r="F6">
         <v>76.47</v>
@@ -808,16 +808,16 @@
         <v>123271.99396875</v>
       </c>
       <c r="H6">
-        <v>149094.02999999947</v>
+        <v>149056.63999999984</v>
       </c>
       <c r="I6">
-        <v>132318.01000000015</v>
+        <v>132543.99000000025</v>
       </c>
       <c r="J6">
-        <v>0.07338257247257117</v>
+        <v>0.0752157544689408</v>
       </c>
       <c r="K6">
-        <v>0.20947203983571058</v>
+        <v>0.2091687268219768</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -903,16 +903,16 @@
         <v>152326.27071875</v>
       </c>
       <c r="H7">
-        <v>118356.71000000056</v>
+        <v>117673.1999999994</v>
       </c>
       <c r="I7">
-        <v>118207.31999999992</v>
+        <v>117941.55000000012</v>
       </c>
       <c r="J7">
-        <v>-0.22398599110816633</v>
+        <v>-0.22573073283095496</v>
       </c>
       <c r="K7">
-        <v>-0.2230052673019854</v>
+        <v>-0.2274924118816828</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>248.21305377072636</v>
       </c>
       <c r="E8">
-        <v>251.09</v>
+        <v>251.2</v>
       </c>
       <c r="F8">
         <v>248.21</v>
@@ -983,16 +983,16 @@
         <v>534514.463140625</v>
       </c>
       <c r="H8">
-        <v>428122.0300000003</v>
+        <v>428122.04999999795</v>
       </c>
       <c r="I8">
-        <v>429528.0100000006</v>
+        <v>430081.95999999996</v>
       </c>
       <c r="J8">
-        <v>-0.19641461621779097</v>
+        <v>-0.195378255112154</v>
       </c>
       <c r="K8">
-        <v>-0.19904500341393758</v>
+        <v>-0.19904496599680668</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>0.9995032250881195</v>
       </c>
       <c r="X8">
-        <v>0.9995017535789453</v>
+        <v>0.9995016873330721</v>
       </c>
       <c r="Y8">
         <v>0.9993532299995422</v>
@@ -1069,7 +1069,7 @@
         <v>226.2261309466292</v>
       </c>
       <c r="E9">
-        <v>229.04</v>
+        <v>229.01</v>
       </c>
       <c r="F9">
         <v>226.23</v>
@@ -1078,16 +1078,16 @@
         <v>423395.234921875</v>
       </c>
       <c r="H9">
-        <v>393199.0500000002</v>
+        <v>392261.38999999827</v>
       </c>
       <c r="I9">
-        <v>391281.87000000034</v>
+        <v>389543.88000000076</v>
       </c>
       <c r="J9">
-        <v>-0.07584725162955654</v>
+        <v>-0.07995213958447242</v>
       </c>
       <c r="K9">
-        <v>-0.07131914209532043</v>
+        <v>-0.07353376314596824</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>0.9561690390110016</v>
       </c>
       <c r="X9">
-        <v>0.9560725586179387</v>
+        <v>0.9560771250046524</v>
       </c>
       <c r="Y9">
         <v>0.934761643409729</v>
@@ -1164,7 +1164,7 @@
         <v>231.6097197762818</v>
       </c>
       <c r="E10">
-        <v>234.73</v>
+        <v>234.77</v>
       </c>
       <c r="F10">
         <v>231.61</v>
@@ -1173,16 +1173,16 @@
         <v>496859.2701875</v>
       </c>
       <c r="H10">
-        <v>400594.0999999989</v>
+        <v>402147.26999999845</v>
       </c>
       <c r="I10">
-        <v>401176.03999999963</v>
+        <v>401645.13000000064</v>
       </c>
       <c r="J10">
-        <v>-0.1925761194943436</v>
+        <v>-0.19163200910303704</v>
       </c>
       <c r="K10">
-        <v>-0.19374735657276443</v>
+        <v>-0.19062138088267938</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>0.9994298815727234</v>
       </c>
       <c r="X10">
-        <v>0.9994294306829894</v>
+        <v>0.9994295056088933</v>
       </c>
       <c r="Y10">
         <v>0.9991127848625183</v>
@@ -1259,7 +1259,7 @@
         <v>149.521593963863</v>
       </c>
       <c r="E11">
-        <v>153.32</v>
+        <v>153.31</v>
       </c>
       <c r="F11">
         <v>149.52</v>
@@ -1268,16 +1268,16 @@
         <v>260256.79878125</v>
       </c>
       <c r="H11">
-        <v>259507.55000000042</v>
+        <v>259590.2899999999</v>
       </c>
       <c r="I11">
-        <v>259059.3099999995</v>
+        <v>259162.89999999962</v>
       </c>
       <c r="J11">
-        <v>-0.004601181551675804</v>
+        <v>-0.004203151604004074</v>
       </c>
       <c r="K11">
-        <v>-0.0028788826449806714</v>
+        <v>-0.002560965878206747</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>0.9758824408054352</v>
       </c>
       <c r="X11">
-        <v>0.9758842138921764</v>
+        <v>0.9758838506156327</v>
       </c>
       <c r="Y11">
         <v>0.9727876782417297</v>
@@ -1354,7 +1354,7 @@
         <v>129.26577895712103</v>
       </c>
       <c r="E12">
-        <v>131.41</v>
+        <v>131.43</v>
       </c>
       <c r="F12">
         <v>129.27</v>
@@ -1363,16 +1363,16 @@
         <v>237021.3285</v>
       </c>
       <c r="H12">
-        <v>224661.42999999988</v>
+        <v>224031.97</v>
       </c>
       <c r="I12">
-        <v>223912.32999999973</v>
+        <v>223035.86000000036</v>
       </c>
       <c r="J12">
-        <v>-0.05530725265511402</v>
+        <v>-0.05900510552576554</v>
       </c>
       <c r="K12">
-        <v>-0.05214677758419587</v>
+        <v>-0.05480248795415895</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>0.9997762739658356</v>
       </c>
       <c r="X12">
-        <v>0.9997757601182167</v>
+        <v>0.9997756994000583</v>
       </c>
       <c r="Y12">
         <v>0.9996004700660706</v>
@@ -1449,7 +1449,7 @@
         <v>444.5994526250636</v>
       </c>
       <c r="E13">
-        <v>479.2</v>
+        <v>448.79</v>
       </c>
       <c r="F13">
         <v>443.97</v>
@@ -1458,16 +1458,16 @@
         <v>787386.3004375</v>
       </c>
       <c r="H13">
-        <v>610410.3900000018</v>
+        <v>577888.1999999993</v>
       </c>
       <c r="I13">
-        <v>573535.6700000006</v>
+        <v>572740.9999999993</v>
       </c>
       <c r="J13">
-        <v>-0.2715955691871656</v>
+        <v>-0.2726048196650565</v>
       </c>
       <c r="K13">
-        <v>-0.2247637663230413</v>
+        <v>-0.2660677488560521</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>0.922089546918869</v>
       </c>
       <c r="X13">
-        <v>0.925163082948467</v>
+        <v>0.9233122720119414</v>
       </c>
       <c r="Y13">
         <v>0.8916369676589966</v>
@@ -1553,16 +1553,16 @@
         <v>2344336.00278125</v>
       </c>
       <c r="H14">
-        <v>1667936.8399999999</v>
+        <v>1667779.1200000017</v>
       </c>
       <c r="I14">
-        <v>1667416.2299999883</v>
+        <v>1667651.879999996</v>
       </c>
       <c r="J14">
-        <v>-0.28874690828370353</v>
+        <v>-0.28864638941621695</v>
       </c>
       <c r="K14">
-        <v>-0.288524836874403</v>
+        <v>-0.2885921139199336</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1633,16 +1633,16 @@
         <v>1154592.063375</v>
       </c>
       <c r="H15">
-        <v>779526.9400000004</v>
+        <v>780118.7799999993</v>
       </c>
       <c r="I15">
-        <v>779789.8600000028</v>
+        <v>779918.7499999973</v>
       </c>
       <c r="J15">
-        <v>-0.3246187248848818</v>
+        <v>-0.32450709238360015</v>
       </c>
       <c r="K15">
-        <v>-0.3248464416762426</v>
+        <v>-0.32433384504685914</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1713,16 +1713,16 @@
         <v>820723.56625</v>
       </c>
       <c r="H16">
-        <v>638084.4700000018</v>
+        <v>635572.4399999996</v>
       </c>
       <c r="I16">
-        <v>593585.1699999982</v>
+        <v>593540.7200000018</v>
       </c>
       <c r="J16">
-        <v>-0.27675383721199664</v>
+        <v>-0.27680799673881445</v>
       </c>
       <c r="K16">
-        <v>-0.22253424144319578</v>
+        <v>-0.2255949918630723</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>162.16593239298544</v>
       </c>
       <c r="E17">
-        <v>124.35</v>
+        <v>163.33</v>
       </c>
       <c r="F17">
         <v>162.17</v>
@@ -1808,16 +1808,16 @@
         <v>229540.2105625</v>
       </c>
       <c r="H17">
-        <v>207189.73999999964</v>
+        <v>290759.820000001</v>
       </c>
       <c r="I17">
-        <v>280578.82999999914</v>
+        <v>281231.42999999935</v>
       </c>
       <c r="J17">
-        <v>0.22235154055329306</v>
+        <v>0.22519461540454017</v>
       </c>
       <c r="K17">
-        <v>-0.09737061104775231</v>
+        <v>0.26670538154286444</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1859,13 +1859,13 @@
         <v>8760</v>
       </c>
       <c r="V17">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W17">
-        <v>0.8857114315032959</v>
+        <v>0.8584362268447876</v>
       </c>
       <c r="X17">
-        <v>0.8483973872519182</v>
+        <v>0.8442560238521953</v>
       </c>
       <c r="Y17">
         <v>0.7737779021263123</v>
@@ -1894,7 +1894,7 @@
         <v>572.2327528927275</v>
       </c>
       <c r="E18">
-        <v>580.2</v>
+        <v>573.74</v>
       </c>
       <c r="F18">
         <v>567.14</v>
@@ -1903,16 +1903,16 @@
         <v>783921.7446875001</v>
       </c>
       <c r="H18">
-        <v>637129.6699999989</v>
+        <v>634580.1400000015</v>
       </c>
       <c r="I18">
-        <v>628291.6699999993</v>
+        <v>629829.9599999988</v>
       </c>
       <c r="J18">
-        <v>-0.19852756444400016</v>
+        <v>-0.19656526398426147</v>
       </c>
       <c r="K18">
-        <v>-0.18725347993251276</v>
+        <v>-0.1905057560905286</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>0.6943569580713908</v>
       </c>
       <c r="X18">
-        <v>0.6422355108723089</v>
+        <v>0.6427299077462565</v>
       </c>
       <c r="Y18">
         <v>0.5385878682136536</v>
@@ -1998,16 +1998,16 @@
         <v>864891.248796875</v>
       </c>
       <c r="H19">
-        <v>741059.1399999994</v>
+        <v>719370.9900000027</v>
       </c>
       <c r="I19">
-        <v>741547.8700000021</v>
+        <v>721780.6400000004</v>
       </c>
       <c r="J19">
-        <v>-0.14261143116947048</v>
+        <v>-0.16546659362775568</v>
       </c>
       <c r="K19">
-        <v>-0.14317650799350184</v>
+        <v>-0.16825266644714157</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2078,16 +2078,16 @@
         <v>164140.983125</v>
       </c>
       <c r="H20">
-        <v>151194.7999999996</v>
+        <v>149727.93000000063</v>
       </c>
       <c r="I20">
-        <v>151205.2299999996</v>
+        <v>150175.43000000017</v>
       </c>
       <c r="J20">
-        <v>-0.07880879521203608</v>
+        <v>-0.08508267014804279</v>
       </c>
       <c r="K20">
-        <v>-0.07887233814812324</v>
+        <v>-0.08780898499933586</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>317.2621596071456</v>
       </c>
       <c r="E21">
-        <v>317.31</v>
+        <v>317.25</v>
       </c>
       <c r="F21">
         <v>317.27</v>
@@ -2158,16 +2158,16 @@
         <v>716679.0925156251</v>
       </c>
       <c r="H21">
-        <v>550825.8900000002</v>
+        <v>551275.5599999999</v>
       </c>
       <c r="I21">
-        <v>550772.5600000004</v>
+        <v>550999.9499999984</v>
       </c>
       <c r="J21">
-        <v>-0.2314934735060763</v>
+        <v>-0.2311761906351614</v>
       </c>
       <c r="K21">
-        <v>-0.2314190608427842</v>
+        <v>-0.2307916252098829</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>335.1360833259603</v>
       </c>
       <c r="E22">
-        <v>342.93</v>
+        <v>342.97</v>
       </c>
       <c r="F22">
         <v>335.14</v>
@@ -2253,16 +2253,16 @@
         <v>677474.1604375</v>
       </c>
       <c r="H22">
-        <v>579357.5900000005</v>
+        <v>574637.4699999978</v>
       </c>
       <c r="I22">
-        <v>566300.8699999999</v>
+        <v>564652.8099999997</v>
       </c>
       <c r="J22">
-        <v>-0.1640996763119445</v>
+        <v>-0.16653232997793213</v>
       </c>
       <c r="K22">
-        <v>-0.14482702982227044</v>
+        <v>-0.15179426233923407</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>0.6806717813014984</v>
       </c>
       <c r="X22">
-        <v>0.6807214940143858</v>
+        <v>0.6807200709235408</v>
       </c>
       <c r="Y22">
         <v>0.6648674011230469</v>
@@ -2339,7 +2339,7 @@
         <v>453.1329202002057</v>
       </c>
       <c r="E23">
-        <v>458.7</v>
+        <v>453.1</v>
       </c>
       <c r="F23">
         <v>445.77</v>
@@ -2348,16 +2348,16 @@
         <v>792440.3724375</v>
       </c>
       <c r="H23">
-        <v>793867.8299999988</v>
+        <v>768009.5999999988</v>
       </c>
       <c r="I23">
-        <v>772580.8299999988</v>
+        <v>764414.879999998</v>
       </c>
       <c r="J23">
-        <v>-0.025061245146324972</v>
+        <v>-0.035366058333571836</v>
       </c>
       <c r="K23">
-        <v>0.0018013438135515139</v>
+        <v>-0.030829792735513478</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2443,16 +2443,16 @@
         <v>585374.201265625</v>
       </c>
       <c r="H24">
-        <v>337161.78000000044</v>
+        <v>336653.07999999996</v>
       </c>
       <c r="I24">
-        <v>335554.3000000009</v>
+        <v>336094.47</v>
       </c>
       <c r="J24">
-        <v>-0.42676957871647536</v>
+        <v>-0.4258468014590712</v>
       </c>
       <c r="K24">
-        <v>-0.424023506210164</v>
+        <v>-0.42489252298422175</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2523,16 +2523,16 @@
         <v>620849.0385625</v>
       </c>
       <c r="H25">
-        <v>492018.9699999989</v>
+        <v>484950.8500000009</v>
       </c>
       <c r="I25">
-        <v>509038.7300000003</v>
+        <v>490437.6700000008</v>
       </c>
       <c r="J25">
-        <v>-0.1800925855041716</v>
+        <v>-0.21005326651459555</v>
       </c>
       <c r="K25">
-        <v>-0.20750627054330528</v>
+        <v>-0.21889087382200792</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>301.58986332378305</v>
       </c>
       <c r="E26">
-        <v>306.38</v>
+        <v>306.25</v>
       </c>
       <c r="F26">
         <v>301.59</v>
@@ -2603,16 +2603,16 @@
         <v>516572.39565625</v>
       </c>
       <c r="H26">
-        <v>428756.9599999993</v>
+        <v>433341.80999999924</v>
       </c>
       <c r="I26">
-        <v>427968.5200000006</v>
+        <v>429651.7699999991</v>
       </c>
       <c r="J26">
-        <v>-0.17152266826741228</v>
+        <v>-0.1682641704960397</v>
       </c>
       <c r="K26">
-        <v>-0.16999637687703106</v>
+        <v>-0.16112085422318242</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>0.8303766846656799</v>
       </c>
       <c r="X26">
-        <v>0.8300490009394313</v>
+        <v>0.8301289730877972</v>
       </c>
       <c r="Y26">
         <v>0.6676775217056274</v>
@@ -2689,7 +2689,7 @@
         <v>378.399470896239</v>
       </c>
       <c r="E27">
-        <v>378.38</v>
+        <v>378.34</v>
       </c>
       <c r="F27">
         <v>349.88</v>
@@ -2698,16 +2698,16 @@
         <v>817752.3991562501</v>
       </c>
       <c r="H27">
-        <v>418347.65999999945</v>
+        <v>421395.20999999874</v>
       </c>
       <c r="I27">
-        <v>384547.71999999945</v>
+        <v>383454.1799999998</v>
       </c>
       <c r="J27">
-        <v>-0.529750422748044</v>
+        <v>-0.5310876734869325</v>
       </c>
       <c r="K27">
-        <v>-0.48841769167336346</v>
+        <v>-0.48469095237777265</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>0.9942453503608704</v>
       </c>
       <c r="X27">
-        <v>0.9942453503608704</v>
+        <v>0.9942453503608703</v>
       </c>
       <c r="Y27">
         <v>0.9942453503608704</v>
@@ -2784,7 +2784,7 @@
         <v>345.96378225826004</v>
       </c>
       <c r="E28">
-        <v>352.34</v>
+        <v>352.35</v>
       </c>
       <c r="F28">
         <v>345.9</v>
@@ -2793,16 +2793,16 @@
         <v>667788.729046875</v>
       </c>
       <c r="H28">
-        <v>605874.350000002</v>
+        <v>597412.1599999983</v>
       </c>
       <c r="I28">
-        <v>600330.1100000013</v>
+        <v>593535.9200000007</v>
       </c>
       <c r="J28">
-        <v>-0.10101790598226545</v>
+        <v>-0.11119206691741297</v>
       </c>
       <c r="K28">
-        <v>-0.09271551967527597</v>
+        <v>-0.10538747658608162</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>0.6806763708591461</v>
       </c>
       <c r="X28">
-        <v>0.6832997491492233</v>
+        <v>0.6833126101435804</v>
       </c>
       <c r="Y28">
         <v>0.5651003122329712</v>
@@ -2888,16 +2888,16 @@
         <v>1310516.2767187501</v>
       </c>
       <c r="H29">
-        <v>1038357.6799999982</v>
+        <v>1034981.9000000011</v>
       </c>
       <c r="I29">
-        <v>1037309.0100000012</v>
+        <v>1038125.9799999995</v>
       </c>
       <c r="J29">
-        <v>-0.20847300531268562</v>
+        <v>-0.20784960977421593</v>
       </c>
       <c r="K29">
-        <v>-0.20767280922307835</v>
+        <v>-0.21024872534099895</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>1001.0919698779919</v>
       </c>
       <c r="E31">
-        <v>1000.78</v>
+        <v>1000.98</v>
       </c>
       <c r="F31">
         <v>985.88</v>
@@ -3048,16 +3048,16 @@
         <v>2056529.9856796875</v>
       </c>
       <c r="H31">
-        <v>1738369.9699999967</v>
+        <v>1737646.0999999994</v>
       </c>
       <c r="I31">
-        <v>1712218.9599999995</v>
+        <v>1711336.940000001</v>
       </c>
       <c r="J31">
-        <v>-0.16742329461629146</v>
+        <v>-0.16785218211423225</v>
       </c>
       <c r="K31">
-        <v>-0.15470720966635368</v>
+        <v>-0.15505919578133273</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>1079.0614351904087</v>
       </c>
       <c r="E32">
-        <v>1192.26</v>
+        <v>1078.87</v>
       </c>
       <c r="F32">
         <v>1088.27</v>
@@ -3143,16 +3143,16 @@
         <v>1969952.347734375</v>
       </c>
       <c r="H32">
-        <v>1698430.8100000003</v>
+        <v>1648427.129999997</v>
       </c>
       <c r="I32">
-        <v>1664666.260000002</v>
+        <v>1667505.560000003</v>
       </c>
       <c r="J32">
-        <v>-0.15497130582142238</v>
+        <v>-0.15353000192223598</v>
       </c>
       <c r="K32">
-        <v>-0.13783152574560964</v>
+        <v>-0.1632147184190324</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>0.9960848093032837</v>
       </c>
       <c r="X32">
-        <v>0.9960848093032837</v>
+        <v>0.9960848093032836</v>
       </c>
       <c r="Y32">
         <v>0.9960848093032837</v>
@@ -3229,7 +3229,7 @@
         <v>269.3035375922859</v>
       </c>
       <c r="E33">
-        <v>273.35</v>
+        <v>273.31</v>
       </c>
       <c r="F33">
         <v>269.31</v>
@@ -3238,16 +3238,16 @@
         <v>563569.372375</v>
       </c>
       <c r="H33">
-        <v>464781.04999999964</v>
+        <v>464640.7000000002</v>
       </c>
       <c r="I33">
-        <v>465237.2100000012</v>
+        <v>465269.9600000003</v>
       </c>
       <c r="J33">
-        <v>-0.17448102610794197</v>
+        <v>-0.17442291436233537</v>
       </c>
       <c r="K33">
-        <v>-0.17529043844005504</v>
+        <v>-0.17553947610405723</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>0.9129302501678467</v>
       </c>
       <c r="X33">
-        <v>0.9130739838926275</v>
+        <v>0.9130418387711657</v>
       </c>
       <c r="Y33">
         <v>0.8371176719665527</v>
@@ -3324,7 +3324,7 @@
         <v>328.7338932952323</v>
       </c>
       <c r="E34">
-        <v>335.56</v>
+        <v>335.49</v>
       </c>
       <c r="F34">
         <v>328.73</v>
@@ -3333,16 +3333,16 @@
         <v>622920.79434375</v>
       </c>
       <c r="H34">
-        <v>503158.3599999998</v>
+        <v>504826.08</v>
       </c>
       <c r="I34">
-        <v>496127.17</v>
+        <v>496871.3499999995</v>
       </c>
       <c r="J34">
-        <v>-0.2035469444832512</v>
+        <v>-0.20235228216541426</v>
       </c>
       <c r="K34">
-        <v>-0.19225949018112404</v>
+        <v>-0.18958223166745192</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>0.995958536863327</v>
       </c>
       <c r="X34">
-        <v>0.9959553334214905</v>
+        <v>0.9959552901379323</v>
       </c>
       <c r="Y34">
         <v>0.9934950470924377</v>
@@ -3419,7 +3419,7 @@
         <v>247.20407091600435</v>
       </c>
       <c r="E35">
-        <v>249.01</v>
+        <v>249.15</v>
       </c>
       <c r="F35">
         <v>247.2</v>
@@ -3428,16 +3428,16 @@
         <v>546679.5353125</v>
       </c>
       <c r="H35">
-        <v>420613.0500000009</v>
+        <v>419201.28000000055</v>
       </c>
       <c r="I35">
-        <v>419271.16000000044</v>
+        <v>419726.69000000064</v>
       </c>
       <c r="J35">
-        <v>-0.2330586149336443</v>
+        <v>-0.232225347963554</v>
       </c>
       <c r="K35">
-        <v>-0.23060399588661262</v>
+        <v>-0.23318644119288032</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>0.9824853241443634</v>
       </c>
       <c r="X35">
-        <v>0.9825190706196454</v>
+        <v>0.9825207532237511</v>
       </c>
       <c r="Y35">
         <v>0.977937638759613</v>
@@ -3514,7 +3514,7 @@
         <v>240.40067946008026</v>
       </c>
       <c r="E36">
-        <v>243.6</v>
+        <v>243.42</v>
       </c>
       <c r="F36">
         <v>235.55</v>
@@ -3523,16 +3523,16 @@
         <v>487335.0708125</v>
       </c>
       <c r="H36">
-        <v>405945.33999999875</v>
+        <v>406553.96999999817</v>
       </c>
       <c r="I36">
-        <v>396909.7599999998</v>
+        <v>397826.9499999986</v>
       </c>
       <c r="J36">
-        <v>-0.18555059183764547</v>
+        <v>-0.1836685397241588</v>
       </c>
       <c r="K36">
-        <v>-0.16700979610764688</v>
+        <v>-0.16576090179149455</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>0.9975154399871826</v>
       </c>
       <c r="X36">
-        <v>0.9974491972552184</v>
+        <v>0.9974486402401913</v>
       </c>
       <c r="Y36">
         <v>0.9955663084983826</v>
@@ -3609,7 +3609,7 @@
         <v>236.5356584716793</v>
       </c>
       <c r="E37">
-        <v>239.9</v>
+        <v>239.79</v>
       </c>
       <c r="F37">
         <v>236.54</v>
@@ -3618,16 +3618,16 @@
         <v>540315.86796875</v>
       </c>
       <c r="H37">
-        <v>413841.58000000124</v>
+        <v>413025.37</v>
       </c>
       <c r="I37">
-        <v>410473.76999999926</v>
+        <v>410503.1199999988</v>
       </c>
       <c r="J37">
-        <v>-0.2403077637843135</v>
+        <v>-0.240253443706486</v>
       </c>
       <c r="K37">
-        <v>-0.23407472455734646</v>
+        <v>-0.23558534093637246</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>0.9297885894775391</v>
       </c>
       <c r="X37">
-        <v>0.9298788034629271</v>
+        <v>0.9298446108120816</v>
       </c>
       <c r="Y37">
         <v>0.8626344799995422</v>
@@ -3704,7 +3704,7 @@
         <v>268.4983597037415</v>
       </c>
       <c r="E38">
-        <v>273.38</v>
+        <v>273.46</v>
       </c>
       <c r="F38">
         <v>268.5</v>
@@ -3713,16 +3713,16 @@
         <v>611161.7611875</v>
       </c>
       <c r="H38">
-        <v>440356.2699999998</v>
+        <v>438914.09999999875</v>
       </c>
       <c r="I38">
-        <v>440886.06000000006</v>
+        <v>435032.6199999983</v>
       </c>
       <c r="J38">
-        <v>-0.27860987385181085</v>
+        <v>-0.28818743640845446</v>
       </c>
       <c r="K38">
-        <v>-0.27947673109590754</v>
+        <v>-0.2818364500632704</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>0.9948030412197113</v>
       </c>
       <c r="X38">
-        <v>0.9948057880780026</v>
+        <v>0.9948078436960466</v>
       </c>
       <c r="Y38">
         <v>0.991644561290741</v>
@@ -3799,7 +3799,7 @@
         <v>288.8784527220046</v>
       </c>
       <c r="E39">
-        <v>293.2</v>
+        <v>293.17</v>
       </c>
       <c r="F39">
         <v>288.88</v>
@@ -3808,16 +3808,16 @@
         <v>621288.2040625</v>
       </c>
       <c r="H39">
-        <v>497048.3499999998</v>
+        <v>496657.939999999</v>
       </c>
       <c r="I39">
-        <v>498588.13999999966</v>
+        <v>499128.5699999983</v>
       </c>
       <c r="J39">
-        <v>-0.19749298837509727</v>
+        <v>-0.19662313442251153</v>
       </c>
       <c r="K39">
-        <v>-0.19997137117704236</v>
+        <v>-0.20059975909338773</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>0.9853409826755524</v>
       </c>
       <c r="X39">
-        <v>0.9853355955112251</v>
+        <v>0.9853379501423905</v>
       </c>
       <c r="Y39">
         <v>0.9732710123062134</v>
@@ -3894,7 +3894,7 @@
         <v>242.67824041891254</v>
       </c>
       <c r="E40">
-        <v>245.59</v>
+        <v>245.63</v>
       </c>
       <c r="F40">
         <v>242.68</v>
@@ -3903,16 +3903,16 @@
         <v>537820.28021875</v>
       </c>
       <c r="H40">
-        <v>417859.14999999997</v>
+        <v>417274.60999999946</v>
       </c>
       <c r="I40">
-        <v>420114.6699999991</v>
+        <v>416694.0600000006</v>
       </c>
       <c r="J40">
-        <v>-0.21885677157967337</v>
+        <v>-0.22521690734585767</v>
       </c>
       <c r="K40">
-        <v>-0.2230505888880905</v>
+        <v>-0.22413745753455128</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>0.9998388588428497</v>
       </c>
       <c r="X40">
-        <v>0.9998353813490123</v>
+        <v>0.9998353816203472</v>
       </c>
       <c r="Y40">
         <v>0.9997027516365051</v>
@@ -3989,7 +3989,7 @@
         <v>306.6488034511967</v>
       </c>
       <c r="E41">
-        <v>309.18</v>
+        <v>309.3</v>
       </c>
       <c r="F41">
         <v>306.65</v>
@@ -3998,16 +3998,16 @@
         <v>609785.8807890625</v>
       </c>
       <c r="H41">
-        <v>483453.2000000005</v>
+        <v>489878.64999999985</v>
       </c>
       <c r="I41">
-        <v>477935.5600000015</v>
+        <v>487231.64000000135</v>
       </c>
       <c r="J41">
-        <v>-0.21622396474389788</v>
+        <v>-0.20097913816973922</v>
       </c>
       <c r="K41">
-        <v>-0.20717547711269996</v>
+        <v>-0.19663825379804262</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>0.9996456801891327</v>
       </c>
       <c r="X41">
-        <v>0.9996449328516457</v>
+        <v>0.999644859550102</v>
       </c>
       <c r="Y41">
         <v>0.9995012283325195</v>
@@ -4084,7 +4084,7 @@
         <v>247.83780582819261</v>
       </c>
       <c r="E42">
-        <v>250.29</v>
+        <v>250.25</v>
       </c>
       <c r="F42">
         <v>247.84</v>
@@ -4093,16 +4093,16 @@
         <v>557910.617875</v>
       </c>
       <c r="H42">
-        <v>426126.98000000045</v>
+        <v>426987.10999999987</v>
       </c>
       <c r="I42">
-        <v>427824.0999999988</v>
+        <v>428327.580000001</v>
       </c>
       <c r="J42">
-        <v>-0.2331673097932456</v>
+        <v>-0.23226487133111365</v>
       </c>
       <c r="K42">
-        <v>-0.23620923074908337</v>
+        <v>-0.23466753218224926</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>0.9999478459358215</v>
       </c>
       <c r="X42">
-        <v>0.9999475514492712</v>
+        <v>0.9999475472411531</v>
       </c>
       <c r="Y42">
         <v>0.9999144077301025</v>
@@ -4179,7 +4179,7 @@
         <v>252.7563713998658</v>
       </c>
       <c r="E43">
-        <v>255.33</v>
+        <v>255.45</v>
       </c>
       <c r="F43">
         <v>252.76</v>
@@ -4188,16 +4188,16 @@
         <v>544122.4698046875</v>
       </c>
       <c r="H43">
-        <v>433006.67000000254</v>
+        <v>423159.5000000014</v>
       </c>
       <c r="I43">
-        <v>435022.22999999806</v>
+        <v>429143.939999999</v>
       </c>
       <c r="J43">
-        <v>-0.20050677165354144</v>
+        <v>-0.21131001968354662</v>
       </c>
       <c r="K43">
-        <v>-0.20421101125371638</v>
+        <v>-0.2223083524709166</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>0.9998289942741394</v>
       </c>
       <c r="X43">
-        <v>0.9998324640728956</v>
+        <v>0.9998324737248678</v>
       </c>
       <c r="Y43">
         <v>0.9996782541275024</v>
@@ -4274,7 +4274,7 @@
         <v>195.3199402770069</v>
       </c>
       <c r="E44">
-        <v>197.82</v>
+        <v>197.81</v>
       </c>
       <c r="F44">
         <v>195.32</v>
@@ -4283,16 +4283,16 @@
         <v>364423.9005625</v>
       </c>
       <c r="H44">
-        <v>335357.7899999994</v>
+        <v>333740.44999999955</v>
       </c>
       <c r="I44">
-        <v>332325.5599999995</v>
+        <v>332598.45000000077</v>
       </c>
       <c r="J44">
-        <v>-0.08807968004556152</v>
+        <v>-0.08733085429735982</v>
       </c>
       <c r="K44">
-        <v>-0.07975906771656888</v>
+        <v>-0.08419714106330446</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>0.9916945695877075</v>
       </c>
       <c r="X44">
-        <v>0.9916944212435462</v>
+        <v>0.9916943848978472</v>
       </c>
       <c r="Y44">
         <v>0.9914849400520325</v>
@@ -4369,7 +4369,7 @@
         <v>175.40979473472862</v>
       </c>
       <c r="E45">
-        <v>179.18</v>
+        <v>179.16</v>
       </c>
       <c r="F45">
         <v>175.38</v>
@@ -4378,16 +4378,16 @@
         <v>382958.01671875</v>
       </c>
       <c r="H45">
-        <v>285765.32000000065</v>
+        <v>285770.9600000002</v>
       </c>
       <c r="I45">
-        <v>284450.15</v>
+        <v>284315.10999999975</v>
       </c>
       <c r="J45">
-        <v>-0.25722889303319013</v>
+        <v>-0.2575815165430916</v>
       </c>
       <c r="K45">
-        <v>-0.25379465235252957</v>
+        <v>-0.2537799248895876</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>0.9857349097728729</v>
       </c>
       <c r="X45">
-        <v>0.9857511165248137</v>
+        <v>0.985750786954611</v>
       </c>
       <c r="Y45">
         <v>0.97918701171875</v>
@@ -4464,7 +4464,7 @@
         <v>186.1016589288956</v>
       </c>
       <c r="E46">
-        <v>188.33</v>
+        <v>188.28</v>
       </c>
       <c r="F46">
         <v>186.1</v>
@@ -4473,16 +4473,16 @@
         <v>332819.311546875</v>
       </c>
       <c r="H46">
-        <v>317373.64000000025</v>
+        <v>317014.3300000006</v>
       </c>
       <c r="I46">
-        <v>315469.7000000013</v>
+        <v>315889.40000000026</v>
       </c>
       <c r="J46">
-        <v>-0.052129221307009824</v>
+        <v>-0.05086817669379828</v>
       </c>
       <c r="K46">
-        <v>-0.0464085797037632</v>
+        <v>-0.04748817450951425</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>0.996557354927063</v>
       </c>
       <c r="X46">
-        <v>0.9965577088431278</v>
+        <v>0.9965575973538644</v>
       </c>
       <c r="Y46">
         <v>0.9948006868362427</v>
@@ -4559,7 +4559,7 @@
         <v>227.72009030719065</v>
       </c>
       <c r="E47">
-        <v>227.85</v>
+        <v>228.02</v>
       </c>
       <c r="F47">
         <v>227.72</v>
@@ -4568,16 +4568,16 @@
         <v>486043.32421875</v>
       </c>
       <c r="H47">
-        <v>372312.0599999991</v>
+        <v>372713.9900000003</v>
       </c>
       <c r="I47">
-        <v>372328.72000000085</v>
+        <v>372413.8600000002</v>
       </c>
       <c r="J47">
-        <v>-0.23395981089037743</v>
+        <v>-0.23378464132059426</v>
       </c>
       <c r="K47">
-        <v>-0.2339940876701861</v>
+        <v>-0.23316714492666174</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>0.998471200466156</v>
       </c>
       <c r="X47">
-        <v>0.9984744672911565</v>
+        <v>0.9984738118372444</v>
       </c>
       <c r="Y47">
         <v>0.9974241256713867</v>
@@ -4663,16 +4663,16 @@
         <v>291893.182875</v>
       </c>
       <c r="H48">
-        <v>240389.39000000025</v>
+        <v>239906.33999999994</v>
       </c>
       <c r="I48">
-        <v>240320.23999999947</v>
+        <v>240351.4599999997</v>
       </c>
       <c r="J48">
-        <v>-0.1766843006302277</v>
+        <v>-0.17657734369586997</v>
       </c>
       <c r="K48">
-        <v>-0.17644739890021918</v>
+        <v>-0.1781022850994874</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>152.48178235119937</v>
       </c>
       <c r="E49">
-        <v>155.39</v>
+        <v>155.41</v>
       </c>
       <c r="F49">
         <v>152.48</v>
@@ -4743,16 +4743,16 @@
         <v>322939.896046875</v>
       </c>
       <c r="H49">
-        <v>264803.3100000003</v>
+        <v>264832.6799999991</v>
       </c>
       <c r="I49">
-        <v>263639.43999999994</v>
+        <v>263870.35000000027</v>
       </c>
       <c r="J49">
-        <v>-0.1836269125393771</v>
+        <v>-0.18291188784646392</v>
       </c>
       <c r="K49">
-        <v>-0.18002292921539842</v>
+        <v>-0.17993198349962172</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>0.9926494359970093</v>
       </c>
       <c r="X49">
-        <v>0.9926497387312103</v>
+        <v>0.992649977044536</v>
       </c>
       <c r="Y49">
         <v>0.9918645620346069</v>
@@ -4829,7 +4829,7 @@
         <v>144.1802737739858</v>
       </c>
       <c r="E50">
-        <v>145.49</v>
+        <v>145.34</v>
       </c>
       <c r="F50">
         <v>144.18</v>
@@ -4838,16 +4838,16 @@
         <v>273733.83790625003</v>
       </c>
       <c r="H50">
-        <v>250687.0600000003</v>
+        <v>250931.79000000012</v>
       </c>
       <c r="I50">
-        <v>249548.9199999996</v>
+        <v>249087.2299999999</v>
       </c>
       <c r="J50">
-        <v>-0.0883519483423654</v>
+        <v>-0.09003858673362572</v>
       </c>
       <c r="K50">
-        <v>-0.08419411382433084</v>
+        <v>-0.08330007017276135</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>0.9979988932609558</v>
       </c>
       <c r="X50">
-        <v>0.9979987605590455</v>
+        <v>0.9979985764506671</v>
       </c>
       <c r="Y50">
         <v>0.9977869987487793</v>
@@ -4924,7 +4924,7 @@
         <v>139.0011435942833</v>
       </c>
       <c r="E51">
-        <v>140.87</v>
+        <v>140.7</v>
       </c>
       <c r="F51">
         <v>139.01</v>
@@ -4933,16 +4933,16 @@
         <v>288687.136953125</v>
       </c>
       <c r="H51">
-        <v>238206.13999999932</v>
+        <v>237736.13999999993</v>
       </c>
       <c r="I51">
-        <v>240392.5500000003</v>
+        <v>240208.95000000068</v>
       </c>
       <c r="J51">
-        <v>-0.1672904011686757</v>
+        <v>-0.16792638378271726</v>
       </c>
       <c r="K51">
-        <v>-0.17486403268921</v>
+        <v>-0.17649209275783614</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>0.9951814115047455</v>
       </c>
       <c r="X51">
-        <v>0.9951860890386104</v>
+        <v>0.9951851847928191</v>
       </c>
       <c r="Y51">
         <v>0.9913647174835205</v>
@@ -5028,16 +5028,16 @@
         <v>298530.688625</v>
       </c>
       <c r="H52">
-        <v>229200.08000000066</v>
+        <v>227658.14999999994</v>
       </c>
       <c r="I52">
-        <v>229696.42</v>
+        <v>229536.0599999999</v>
       </c>
       <c r="J52">
-        <v>-0.23057685942454753</v>
+        <v>-0.23111402362946964</v>
       </c>
       <c r="K52">
-        <v>-0.23223946906205395</v>
+        <v>-0.23740453268449987</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>175.56254732794577</v>
       </c>
       <c r="E53">
-        <v>178.28</v>
+        <v>178.26</v>
       </c>
       <c r="F53">
         <v>175.49</v>
@@ -5108,16 +5108,16 @@
         <v>379638.374875</v>
       </c>
       <c r="H53">
-        <v>292232.4600000003</v>
+        <v>288087.9800000004</v>
       </c>
       <c r="I53">
-        <v>291270.07000000105</v>
+        <v>290426.30999999866</v>
       </c>
       <c r="J53">
-        <v>-0.2327696848457302</v>
+        <v>-0.2349922209638985</v>
       </c>
       <c r="K53">
-        <v>-0.23023466714548813</v>
+        <v>-0.24115158248989857</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>0.9989336729049683</v>
       </c>
       <c r="X53">
-        <v>0.9989336777898338</v>
+        <v>0.9989337228298278</v>
       </c>
       <c r="Y53">
         <v>0.9987096786499023</v>
@@ -5194,7 +5194,7 @@
         <v>209.88418712796846</v>
       </c>
       <c r="E54">
-        <v>211.67</v>
+        <v>211.72</v>
       </c>
       <c r="F54">
         <v>209.85</v>
@@ -5203,16 +5203,16 @@
         <v>407601.3085625</v>
       </c>
       <c r="H54">
-        <v>360228.03999999986</v>
+        <v>355458.8699999995</v>
       </c>
       <c r="I54">
-        <v>359045.11000000004</v>
+        <v>345875.8400000014</v>
       </c>
       <c r="J54">
-        <v>-0.11912669940571237</v>
+        <v>-0.1514358940116941</v>
       </c>
       <c r="K54">
-        <v>-0.1162245252096292</v>
+        <v>-0.1279251009924204</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>0.9964922070503235</v>
       </c>
       <c r="X54">
-        <v>0.9964898725058446</v>
+        <v>0.9964900994657013</v>
       </c>
       <c r="Y54">
         <v>0.9954447746276855</v>
@@ -5289,7 +5289,7 @@
         <v>123.45617746409927</v>
       </c>
       <c r="E55">
-        <v>124.5</v>
+        <v>124.43</v>
       </c>
       <c r="F55">
         <v>123.46</v>
@@ -5298,16 +5298,16 @@
         <v>228267.10915625</v>
       </c>
       <c r="H55">
-        <v>214082.11000000004</v>
+        <v>213070.25000000017</v>
       </c>
       <c r="I55">
-        <v>212674.50999999986</v>
+        <v>211444.91000000056</v>
       </c>
       <c r="J55">
-        <v>-0.06830856716013745</v>
+        <v>-0.07369523896118804</v>
       </c>
       <c r="K55">
-        <v>-0.06214210715105804</v>
+        <v>-0.06657489645539556</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>0.9970032274723053</v>
       </c>
       <c r="X55">
-        <v>0.9970023711082907</v>
+        <v>0.9970029310708326</v>
       </c>
       <c r="Y55">
         <v>0.9948603510856628</v>
@@ -5384,7 +5384,7 @@
         <v>194.27060199805737</v>
       </c>
       <c r="E56">
-        <v>196.51</v>
+        <v>196.54</v>
       </c>
       <c r="F56">
         <v>194.27</v>
@@ -5393,16 +5393,16 @@
         <v>409701.58296875004</v>
       </c>
       <c r="H56">
-        <v>324235.5800000002</v>
+        <v>324692.46000000095</v>
       </c>
       <c r="I56">
-        <v>324008.80999999953</v>
+        <v>324047.1699999985</v>
       </c>
       <c r="J56">
-        <v>-0.20915899896653978</v>
+        <v>-0.20906536984331056</v>
       </c>
       <c r="K56">
-        <v>-0.20860549854226157</v>
+        <v>-0.2074903454186389</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>0.9994361400604248</v>
       </c>
       <c r="X56">
-        <v>0.999422717082053</v>
+        <v>0.9994227655990708</v>
       </c>
       <c r="Y56">
         <v>0.9991068243980408</v>
@@ -5479,7 +5479,7 @@
         <v>295.2224779187909</v>
       </c>
       <c r="E57">
-        <v>298.31</v>
+        <v>298.36</v>
       </c>
       <c r="F57">
         <v>295.22</v>
@@ -5488,16 +5488,16 @@
         <v>610238.6749375</v>
       </c>
       <c r="H57">
-        <v>503886.8499999998</v>
+        <v>501930.16000000003</v>
       </c>
       <c r="I57">
-        <v>499558.8799999986</v>
+        <v>490228.42000000086</v>
       </c>
       <c r="J57">
-        <v>-0.18137132155518843</v>
+        <v>-0.19666117515378798</v>
       </c>
       <c r="K57">
-        <v>-0.17427906375877056</v>
+        <v>-0.1774854977007035</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>0.9927153289318085</v>
       </c>
       <c r="X57">
-        <v>0.9927155117233776</v>
+        <v>0.9927156490868065</v>
       </c>
       <c r="Y57">
         <v>0.9925351142883301</v>
@@ -5583,16 +5583,16 @@
         <v>1071025.59009375</v>
       </c>
       <c r="H58">
-        <v>767935.3900000005</v>
+        <v>777212.3699999994</v>
       </c>
       <c r="I58">
-        <v>792616.2200000007</v>
+        <v>799081.2600000009</v>
       </c>
       <c r="J58">
-        <v>-0.2599465154416893</v>
+        <v>-0.25391020775698275</v>
       </c>
       <c r="K58">
-        <v>-0.2829906240309526</v>
+        <v>-0.2743288515338203</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>255.2397724816858</v>
       </c>
       <c r="E59">
-        <v>256.19</v>
+        <v>256.12</v>
       </c>
       <c r="F59">
         <v>255.24</v>
@@ -5663,16 +5663,16 @@
         <v>533733.1774375</v>
       </c>
       <c r="H59">
-        <v>438379.5099999997</v>
+        <v>441995.4099999998</v>
       </c>
       <c r="I59">
-        <v>439164.06</v>
+        <v>434035.71000000025</v>
       </c>
       <c r="J59">
-        <v>-0.17718425879300712</v>
+        <v>-0.18679271151206311</v>
       </c>
       <c r="K59">
-        <v>-0.17865418802575028</v>
+        <v>-0.17187945459553647</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>0.999303787946701</v>
       </c>
       <c r="X59">
-        <v>0.9993035601980813</v>
+        <v>0.9993037315225282</v>
       </c>
       <c r="Y59">
         <v>0.9989370703697205</v>
@@ -5749,7 +5749,7 @@
         <v>226.51910467834284</v>
       </c>
       <c r="E60">
-        <v>227.12</v>
+        <v>227.17</v>
       </c>
       <c r="F60">
         <v>226.52</v>
@@ -5758,16 +5758,16 @@
         <v>482360.46084375</v>
       </c>
       <c r="H60">
-        <v>390339.2500000012</v>
+        <v>391172.45000000024</v>
       </c>
       <c r="I60">
-        <v>390765.00999999937</v>
+        <v>389888.6399999998</v>
       </c>
       <c r="J60">
-        <v>-0.1898900475456278</v>
+        <v>-0.1917068838561053</v>
       </c>
       <c r="K60">
-        <v>-0.190772706956089</v>
+        <v>-0.18904536803087615</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>0.9990383982658386</v>
       </c>
       <c r="X60">
-        <v>0.99903911371521</v>
+        <v>0.9990389344033692</v>
       </c>
       <c r="Y60">
         <v>0.9984740614891052</v>
@@ -5853,16 +5853,16 @@
         <v>505885.22665625</v>
       </c>
       <c r="H61">
-        <v>408586.0600000014</v>
+        <v>409025.27999999846</v>
       </c>
       <c r="I61">
-        <v>408959.4499999999</v>
+        <v>408760.5999999989</v>
       </c>
       <c r="J61">
-        <v>-0.1915963771009889</v>
+        <v>-0.19198945044949386</v>
       </c>
       <c r="K61">
-        <v>-0.19233446941980695</v>
+        <v>-0.19146624877043125</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -5933,16 +5933,16 @@
         <v>486572.18503125</v>
       </c>
       <c r="H62">
-        <v>391158.93000000063</v>
+        <v>391210.6000000003</v>
       </c>
       <c r="I62">
-        <v>387866.34999999957</v>
+        <v>386912.2299999996</v>
       </c>
       <c r="J62">
-        <v>-0.20285959219989336</v>
+        <v>-0.20482049343788483</v>
       </c>
       <c r="K62">
-        <v>-0.19609270313123525</v>
+        <v>-0.19598651128223676</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>0.9955373108386993</v>
       </c>
       <c r="X62">
-        <v>0.9955416569818425</v>
+        <v>0.9955422285558855</v>
       </c>
       <c r="Y62">
         <v>0.993509829044342</v>
@@ -6019,7 +6019,7 @@
         <v>236.66895341526262</v>
       </c>
       <c r="E63">
-        <v>238.01</v>
+        <v>238.08</v>
       </c>
       <c r="F63">
         <v>236.67</v>
@@ -6028,16 +6028,16 @@
         <v>513533.8045</v>
       </c>
       <c r="H63">
-        <v>404494.8999999999</v>
+        <v>404207.1400000021</v>
       </c>
       <c r="I63">
-        <v>402982.08000000106</v>
+        <v>402430.0199999998</v>
       </c>
       <c r="J63">
-        <v>-0.21527643074565883</v>
+        <v>-0.21635145247775064</v>
       </c>
       <c r="K63">
-        <v>-0.21233052925535326</v>
+        <v>-0.2128908818504039</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>0.9935329854488373</v>
       </c>
       <c r="X63">
-        <v>0.9935127544076804</v>
+        <v>0.9935143981311432</v>
       </c>
       <c r="Y63">
         <v>0.9906347393989563</v>
@@ -6114,7 +6114,7 @@
         <v>259.5526405094437</v>
       </c>
       <c r="E64">
-        <v>260.77</v>
+        <v>260.69</v>
       </c>
       <c r="F64">
         <v>259.25</v>
@@ -6123,16 +6123,16 @@
         <v>490208.117640625</v>
       </c>
       <c r="H64">
-        <v>429632.4499999995</v>
+        <v>427733.2000000002</v>
       </c>
       <c r="I64">
-        <v>427017.77000000037</v>
+        <v>423337.96999999956</v>
       </c>
       <c r="J64">
-        <v>-0.1289051432782472</v>
+        <v>-0.13641175091606378</v>
       </c>
       <c r="K64">
-        <v>-0.12357132707670489</v>
+        <v>-0.1274457019221081</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>0.990566611289978</v>
       </c>
       <c r="X64">
-        <v>0.9905832181348349</v>
+        <v>0.9905835666469972</v>
       </c>
       <c r="Y64">
         <v>0.9871810078620911</v>
@@ -6209,7 +6209,7 @@
         <v>212.50050926076128</v>
       </c>
       <c r="E65">
-        <v>162.27</v>
+        <v>214.07</v>
       </c>
       <c r="F65">
         <v>212.5</v>
@@ -6218,16 +6218,16 @@
         <v>454332.82478125003</v>
       </c>
       <c r="H65">
-        <v>269321.8999999999</v>
+        <v>367973.09000000084</v>
       </c>
       <c r="I65">
-        <v>365402.51</v>
+        <v>365221.6700000002</v>
       </c>
       <c r="J65">
-        <v>-0.19573825603304748</v>
+        <v>-0.19613629022766432</v>
       </c>
       <c r="K65">
-        <v>-0.40721452356062604</v>
+        <v>-0.19008033333895533</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -6269,16 +6269,16 @@
         <v>8760</v>
       </c>
       <c r="V65">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W65">
-        <v>0.9486021101474762</v>
+        <v>0.904600977897644</v>
       </c>
       <c r="X65">
-        <v>0.940790184744351</v>
+        <v>0.8822494065456982</v>
       </c>
       <c r="Y65">
-        <v>0.9253217577934265</v>
+        <v>0.8165987133979797</v>
       </c>
       <c r="Z65">
         <v>0.9718824625015259</v>
@@ -6304,7 +6304,7 @@
         <v>198.9995682565251</v>
       </c>
       <c r="E66">
-        <v>202.47</v>
+        <v>202.51</v>
       </c>
       <c r="F66">
         <v>199.0</v>
@@ -6313,16 +6313,16 @@
         <v>425120.37759375</v>
       </c>
       <c r="H66">
-        <v>336498.71999999986</v>
+        <v>336452.89000000054</v>
       </c>
       <c r="I66">
-        <v>333591.6599999998</v>
+        <v>332334.0899999991</v>
       </c>
       <c r="J66">
-        <v>-0.21530070638301918</v>
+        <v>-0.21825885674767295</v>
       </c>
       <c r="K66">
-        <v>-0.2084625020690917</v>
+        <v>-0.2085703068284371</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>0.9685877561569214</v>
       </c>
       <c r="X66">
-        <v>0.9686021328869383</v>
+        <v>0.9686100405483101</v>
       </c>
       <c r="Y66">
         <v>0.9416994452476501</v>
@@ -6408,16 +6408,16 @@
         <v>494740.905765625</v>
       </c>
       <c r="H67">
-        <v>396793.38000000047</v>
+        <v>378545.73999999947</v>
       </c>
       <c r="I67">
-        <v>385289.2900000003</v>
+        <v>389067.16999999987</v>
       </c>
       <c r="J67">
-        <v>-0.22123017217718297</v>
+        <v>-0.2135940944727264</v>
       </c>
       <c r="K67">
-        <v>-0.19797741529790847</v>
+        <v>-0.23486064000673315</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>0.9971413910388947</v>
       </c>
       <c r="X67">
-        <v>0.997141775228023</v>
+        <v>0.9971416718475813</v>
       </c>
       <c r="Y67">
         <v>0.9969078898429871</v>
@@ -6494,7 +6494,7 @@
         <v>218.78038222249367</v>
       </c>
       <c r="E68">
-        <v>220.0</v>
+        <v>219.95</v>
       </c>
       <c r="F68">
         <v>218.78</v>
@@ -6503,16 +6503,16 @@
         <v>502089.816375</v>
       </c>
       <c r="H68">
-        <v>367620.42000000045</v>
+        <v>365506.03000000044</v>
       </c>
       <c r="I68">
-        <v>366178.9299999992</v>
+        <v>341743.5200000008</v>
       </c>
       <c r="J68">
-        <v>-0.27069038634611925</v>
+        <v>-0.3193577944533335</v>
       </c>
       <c r="K68">
-        <v>-0.26781940598963927</v>
+        <v>-0.2720305848087309</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>0.9925515353679657</v>
       </c>
       <c r="X68">
-        <v>0.9925514179749969</v>
+        <v>0.9925494402195629</v>
       </c>
       <c r="Y68">
         <v>0.9868566393852234</v>
@@ -6589,7 +6589,7 @@
         <v>225.0414054966589</v>
       </c>
       <c r="E69">
-        <v>226.55</v>
+        <v>226.59</v>
       </c>
       <c r="F69">
         <v>225.04</v>
@@ -6598,16 +6598,16 @@
         <v>480000.2721875</v>
       </c>
       <c r="H69">
-        <v>383901.46000000107</v>
+        <v>373751.5200000004</v>
       </c>
       <c r="I69">
-        <v>376456.0799999994</v>
+        <v>383653.14000000025</v>
       </c>
       <c r="J69">
-        <v>-0.21571694473342656</v>
+        <v>-0.20072307823580607</v>
       </c>
       <c r="K69">
-        <v>-0.2002057451958285</v>
+        <v>-0.22135144153834188</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>0.9872180819511414</v>
       </c>
       <c r="X69">
-        <v>0.9872134955960788</v>
+        <v>0.9872188656111406</v>
       </c>
       <c r="Y69">
         <v>0.9779108166694641</v>
@@ -6684,7 +6684,7 @@
         <v>218.95301297106866</v>
       </c>
       <c r="E70">
-        <v>220.27</v>
+        <v>220.12</v>
       </c>
       <c r="F70">
         <v>218.95</v>
@@ -6693,16 +6693,16 @@
         <v>508592.4428125</v>
       </c>
       <c r="H70">
-        <v>360828.1099999991</v>
+        <v>361309.1299999998</v>
       </c>
       <c r="I70">
-        <v>361675.07999999874</v>
+        <v>361069.2200000008</v>
       </c>
       <c r="J70">
-        <v>-0.28887051879900716</v>
+        <v>-0.29006176732925976</v>
       </c>
       <c r="K70">
-        <v>-0.2905358404371265</v>
+        <v>-0.2895900536744671</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>0.998975396156311</v>
       </c>
       <c r="X70">
-        <v>0.9989751882895327</v>
+        <v>0.9989750391983503</v>
       </c>
       <c r="Y70">
         <v>0.9985682964324951</v>
@@ -6779,7 +6779,7 @@
         <v>228.10057563581836</v>
       </c>
       <c r="E71">
-        <v>229.16</v>
+        <v>229.22</v>
       </c>
       <c r="F71">
         <v>228.1</v>
@@ -6788,16 +6788,16 @@
         <v>479679.00865625</v>
       </c>
       <c r="H71">
-        <v>382731.6600000003</v>
+        <v>366946.7199999997</v>
       </c>
       <c r="I71">
-        <v>376075.9499999998</v>
+        <v>385815.82</v>
       </c>
       <c r="J71">
-        <v>-0.2159841410331441</v>
+        <v>-0.19567916661434465</v>
       </c>
       <c r="K71">
-        <v>-0.20210879964881806</v>
+        <v>-0.23501609747746355</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>0.9883751571178436</v>
       </c>
       <c r="X71">
-        <v>0.9883810478855173</v>
+        <v>0.9883806654337303</v>
       </c>
       <c r="Y71">
         <v>0.9821122884750366</v>
@@ -6874,7 +6874,7 @@
         <v>202.0044162388469</v>
       </c>
       <c r="E72">
-        <v>203.05</v>
+        <v>202.96</v>
       </c>
       <c r="F72">
         <v>202.0</v>
@@ -6883,16 +6883,16 @@
         <v>458935.75946875004</v>
       </c>
       <c r="H72">
-        <v>332127.69999999955</v>
+        <v>331271.36999999953</v>
       </c>
       <c r="I72">
-        <v>330575.0800000004</v>
+        <v>330892.89000000193</v>
       </c>
       <c r="J72">
-        <v>-0.27969204146858373</v>
+        <v>-0.278999548034711</v>
       </c>
       <c r="K72">
-        <v>-0.2763089536006948</v>
+        <v>-0.27817485744961534</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>0.9989030957221985</v>
       </c>
       <c r="X72">
-        <v>0.9989030213242698</v>
+        <v>0.9989029534482735</v>
       </c>
       <c r="Y72">
         <v>0.9986801743507385</v>
@@ -6969,7 +6969,7 @@
         <v>252.26921306743066</v>
       </c>
       <c r="E73">
-        <v>254.82</v>
+        <v>254.86</v>
       </c>
       <c r="F73">
         <v>252.27</v>
@@ -6978,16 +6978,16 @@
         <v>525984.14640625</v>
       </c>
       <c r="H73">
-        <v>430784.1899999998</v>
+        <v>417148.4499999999</v>
       </c>
       <c r="I73">
-        <v>423589.0700000003</v>
+        <v>426815.9299999994</v>
       </c>
       <c r="J73">
-        <v>-0.19467331307579683</v>
+        <v>-0.18853841334156263</v>
       </c>
       <c r="K73">
-        <v>-0.18099396542024546</v>
+        <v>-0.2069182068506482</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>0.9837775528430939</v>
       </c>
       <c r="X73">
-        <v>0.98374819680919</v>
+        <v>0.9837520337965314</v>
       </c>
       <c r="Y73">
         <v>0.9707536101341248</v>
@@ -7064,7 +7064,7 @@
         <v>229.29124711328245</v>
       </c>
       <c r="E74">
-        <v>231.99</v>
+        <v>231.98</v>
       </c>
       <c r="F74">
         <v>229.29</v>
@@ -7073,16 +7073,16 @@
         <v>516358.172625</v>
       </c>
       <c r="H74">
-        <v>377380.9800000002</v>
+        <v>378391.4100000003</v>
       </c>
       <c r="I74">
-        <v>377251.1200000005</v>
+        <v>377272.1799999995</v>
       </c>
       <c r="J74">
-        <v>-0.26940031164380274</v>
+        <v>-0.2693595260009766</v>
       </c>
       <c r="K74">
-        <v>-0.2691488195460994</v>
+        <v>-0.26719198017845003</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>0.9955041408538818</v>
       </c>
       <c r="X74">
-        <v>0.9955018882777119</v>
+        <v>0.9955029786408991</v>
       </c>
       <c r="Y74">
         <v>0.9924845099449158</v>
@@ -7159,7 +7159,7 @@
         <v>182.37776185766984</v>
       </c>
       <c r="E75">
-        <v>185.79</v>
+        <v>185.8</v>
       </c>
       <c r="F75">
         <v>182.38</v>
@@ -7168,16 +7168,16 @@
         <v>377544.4115</v>
       </c>
       <c r="H75">
-        <v>311967.9599999997</v>
+        <v>312353.72000000114</v>
       </c>
       <c r="I75">
-        <v>310949.8999999995</v>
+        <v>310862.3399999989</v>
       </c>
       <c r="J75">
-        <v>-0.17638855051626287</v>
+        <v>-0.17662047025161984</v>
       </c>
       <c r="K75">
-        <v>-0.1736920200711283</v>
+        <v>-0.172670259482834</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>0.9920589327812195</v>
       </c>
       <c r="X75">
-        <v>0.9920543375740819</v>
+        <v>0.9920539874987864</v>
       </c>
       <c r="Y75">
         <v>0.9865856170654297</v>
@@ -7254,7 +7254,7 @@
         <v>230.8582433570467</v>
       </c>
       <c r="E76">
-        <v>232.78</v>
+        <v>232.79</v>
       </c>
       <c r="F76">
         <v>230.83</v>
@@ -7263,16 +7263,16 @@
         <v>525665.94009375</v>
       </c>
       <c r="H76">
-        <v>358066.47000000026</v>
+        <v>359145.3000000011</v>
       </c>
       <c r="I76">
-        <v>360974.28000000014</v>
+        <v>359911.8199999996</v>
       </c>
       <c r="J76">
-        <v>-0.3133009912424189</v>
+        <v>-0.3153221608084194</v>
       </c>
       <c r="K76">
-        <v>-0.31883266027062585</v>
+        <v>-0.3167803492538451</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>0.9873211681842804</v>
       </c>
       <c r="X76">
-        <v>0.9873186737420969</v>
+        <v>0.9873193475551016</v>
       </c>
       <c r="Y76">
         <v>0.9858280420303345</v>
@@ -7349,7 +7349,7 @@
         <v>189.9355324422919</v>
       </c>
       <c r="E77">
-        <v>192.19</v>
+        <v>192.3</v>
       </c>
       <c r="F77">
         <v>189.94</v>
@@ -7358,16 +7358,16 @@
         <v>381597.49453125003</v>
       </c>
       <c r="H77">
-        <v>326117.9299999991</v>
+        <v>325126.2999999996</v>
       </c>
       <c r="I77">
-        <v>323992.5499999992</v>
+        <v>324190.18999999977</v>
       </c>
       <c r="J77">
-        <v>-0.15095734473312544</v>
+        <v>-0.1504394168042658</v>
       </c>
       <c r="K77">
-        <v>-0.14538765407619192</v>
+        <v>-0.14798628224909868</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>0.9964025914669037</v>
       </c>
       <c r="X77">
-        <v>0.9964003101408118</v>
+        <v>0.9963997689935021</v>
       </c>
       <c r="Y77">
         <v>0.9938947558403015</v>
@@ -7444,7 +7444,7 @@
         <v>270.8078188346374</v>
       </c>
       <c r="E78">
-        <v>272.57</v>
+        <v>272.81</v>
       </c>
       <c r="F78">
         <v>270.81</v>
@@ -7453,16 +7453,16 @@
         <v>573449.410859375</v>
       </c>
       <c r="H78">
-        <v>437053.7900000016</v>
+        <v>438069.8100000007</v>
       </c>
       <c r="I78">
-        <v>436858.0800000001</v>
+        <v>438703.5099999998</v>
       </c>
       <c r="J78">
-        <v>-0.23819246872130934</v>
+        <v>-0.23497434700899625</v>
       </c>
       <c r="K78">
-        <v>-0.23785118316709064</v>
+        <v>-0.23607941397392593</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>0.9877824187278748</v>
       </c>
       <c r="X78">
-        <v>0.9877847510732445</v>
+        <v>0.9877857545271124</v>
       </c>
       <c r="Y78">
         <v>0.9835785627365112</v>
@@ -7539,7 +7539,7 @@
         <v>182.02623338301825</v>
       </c>
       <c r="E79">
-        <v>184.57</v>
+        <v>184.54</v>
       </c>
       <c r="F79">
         <v>182.03</v>
@@ -7548,16 +7548,16 @@
         <v>414822.39353125</v>
       </c>
       <c r="H79">
-        <v>309115.5399999991</v>
+        <v>308491.0600000007</v>
       </c>
       <c r="I79">
-        <v>308339.93000000017</v>
+        <v>307722.18999999977</v>
       </c>
       <c r="J79">
-        <v>-0.256694106180717</v>
+        <v>-0.25818327361630733</v>
       </c>
       <c r="K79">
-        <v>-0.25482436623394983</v>
+        <v>-0.25632978158696973</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>0.9977971613407135</v>
       </c>
       <c r="X79">
-        <v>0.9977972517185442</v>
+        <v>0.9977972894209476</v>
       </c>
       <c r="Y79">
         <v>0.9975584745407104</v>
@@ -7634,7 +7634,7 @@
         <v>161.54929316011675</v>
       </c>
       <c r="E80">
-        <v>162.47</v>
+        <v>162.34</v>
       </c>
       <c r="F80">
         <v>161.54</v>
@@ -7643,16 +7643,16 @@
         <v>344803.76340625</v>
       </c>
       <c r="H80">
-        <v>258080.5900000002</v>
+        <v>258627.14999999944</v>
       </c>
       <c r="I80">
-        <v>258196.4700000007</v>
+        <v>258300.07000000036</v>
       </c>
       <c r="J80">
-        <v>-0.2511785038268507</v>
+        <v>-0.25087804306918315</v>
       </c>
       <c r="K80">
-        <v>-0.25151457904498564</v>
+        <v>-0.2499294455342609</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>0.994592696428299</v>
       </c>
       <c r="X80">
-        <v>0.9945929110650309</v>
+        <v>0.9945931405754254</v>
       </c>
       <c r="Y80">
         <v>0.993884265422821</v>
@@ -7729,7 +7729,7 @@
         <v>228.00089313279236</v>
       </c>
       <c r="E81">
-        <v>230.4</v>
+        <v>230.34</v>
       </c>
       <c r="F81">
         <v>228.0</v>
@@ -7738,16 +7738,16 @@
         <v>499807.21021875</v>
       </c>
       <c r="H81">
-        <v>386784.2599999995</v>
+        <v>385527.7600000005</v>
       </c>
       <c r="I81">
-        <v>383625.7999999992</v>
+        <v>385337.69000000035</v>
       </c>
       <c r="J81">
-        <v>-0.23245244935122455</v>
+        <v>-0.2290273487024125</v>
       </c>
       <c r="K81">
-        <v>-0.22613309273646512</v>
+        <v>-0.22864706207165955</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>0.982245534658432</v>
       </c>
       <c r="X81">
-        <v>0.9822338705884137</v>
+        <v>0.9822298075540233</v>
       </c>
       <c r="Y81">
         <v>0.9719430208206177</v>
@@ -7824,7 +7824,7 @@
         <v>214.3274098047559</v>
       </c>
       <c r="E82">
-        <v>217.77</v>
+        <v>217.69</v>
       </c>
       <c r="F82">
         <v>214.33</v>
@@ -7833,16 +7833,16 @@
         <v>437326.23128125</v>
       </c>
       <c r="H82">
-        <v>325723.64000000036</v>
+        <v>326802.32999999856</v>
       </c>
       <c r="I82">
-        <v>325703.1399999997</v>
+        <v>315429.36000000004</v>
       </c>
       <c r="J82">
-        <v>-0.2552398719697746</v>
+        <v>-0.2787321284710602</v>
       </c>
       <c r="K82">
-        <v>-0.25519299620853664</v>
+        <v>-0.2527264393847259</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>0.9951616823673248</v>
       </c>
       <c r="X82">
-        <v>0.9951601786296322</v>
+        <v>0.9951610530012801</v>
       </c>
       <c r="Y82">
         <v>0.9916424751281738</v>
@@ -7919,7 +7919,7 @@
         <v>217.127566230635</v>
       </c>
       <c r="E83">
-        <v>219.56</v>
+        <v>219.69</v>
       </c>
       <c r="F83">
         <v>217.11</v>
@@ -7928,16 +7928,16 @@
         <v>446134.701671875</v>
       </c>
       <c r="H83">
-        <v>373511.5599999998</v>
+        <v>372113.70000000007</v>
       </c>
       <c r="I83">
-        <v>371669.7700000003</v>
+        <v>360601.9599999996</v>
       </c>
       <c r="J83">
-        <v>-0.16691131936793943</v>
+        <v>-0.19171954423483376</v>
       </c>
       <c r="K83">
-        <v>-0.1627829922212336</v>
+        <v>-0.165916261152705</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>0.9696769714355469</v>
       </c>
       <c r="X83">
-        <v>0.9696835103507995</v>
+        <v>0.969682511998458</v>
       </c>
       <c r="Y83">
         <v>0.965145468711853</v>
@@ -8014,7 +8014,7 @@
         <v>249.443313773792</v>
       </c>
       <c r="E84">
-        <v>255.51</v>
+        <v>255.59</v>
       </c>
       <c r="F84">
         <v>249.44</v>
@@ -8023,16 +8023,16 @@
         <v>540011.94325</v>
       </c>
       <c r="H84">
-        <v>420603.47999999905</v>
+        <v>420961.5699999994</v>
       </c>
       <c r="I84">
-        <v>418727.6800000006</v>
+        <v>418173.2000000006</v>
       </c>
       <c r="J84">
-        <v>-0.22459552009176684</v>
+        <v>-0.22562231219688753</v>
       </c>
       <c r="K84">
-        <v>-0.2211218932147219</v>
+        <v>-0.22045877825129118</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>0.9955606162548065</v>
       </c>
       <c r="X84">
-        <v>0.9955258693961518</v>
+        <v>0.9955270799754836</v>
       </c>
       <c r="Y84">
         <v>0.9919151067733765</v>
@@ -8109,7 +8109,7 @@
         <v>189.8420517087396</v>
       </c>
       <c r="E85">
-        <v>192.33</v>
+        <v>192.28</v>
       </c>
       <c r="F85">
         <v>183.47</v>
@@ -8118,16 +8118,16 @@
         <v>388141.38653125</v>
       </c>
       <c r="H85">
-        <v>328074.5599999982</v>
+        <v>327905.72000000055</v>
       </c>
       <c r="I85">
-        <v>316196.2799999989</v>
+        <v>315718.82</v>
       </c>
       <c r="J85">
-        <v>-0.18535798816563115</v>
+        <v>-0.18658810692278274</v>
       </c>
       <c r="K85">
-        <v>-0.15475501612455783</v>
+        <v>-0.15519001225188797</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>0.9867531955242157</v>
       </c>
       <c r="X85">
-        <v>0.9867472940499561</v>
+        <v>0.9867467937375566</v>
       </c>
       <c r="Y85">
         <v>0.9838072061538696</v>
@@ -8204,7 +8204,7 @@
         <v>156.63172932768933</v>
       </c>
       <c r="E86">
-        <v>159.91</v>
+        <v>159.94</v>
       </c>
       <c r="F86">
         <v>156.63</v>
@@ -8213,16 +8213,16 @@
         <v>328101.60225</v>
       </c>
       <c r="H86">
-        <v>270855.72</v>
+        <v>269512.65999999933</v>
       </c>
       <c r="I86">
-        <v>270034.6800000006</v>
+        <v>268630.5600000002</v>
       </c>
       <c r="J86">
-        <v>-0.176978478165903</v>
+        <v>-0.18125800618518567</v>
       </c>
       <c r="K86">
-        <v>-0.17447608258365346</v>
+        <v>-0.17856950971351332</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>0.9736452400684357</v>
       </c>
       <c r="X86">
-        <v>0.9736423435949314</v>
+        <v>0.9736436572946708</v>
       </c>
       <c r="Y86">
         <v>0.9703617095947266</v>
@@ -8299,7 +8299,7 @@
         <v>146.53470417120252</v>
       </c>
       <c r="E87">
-        <v>147.6</v>
+        <v>147.71</v>
       </c>
       <c r="F87">
         <v>146.53</v>
@@ -8308,16 +8308,16 @@
         <v>253518.4709453125</v>
       </c>
       <c r="H87">
-        <v>250179.39000000036</v>
+        <v>250661.94999999952</v>
       </c>
       <c r="I87">
-        <v>249722.8199999989</v>
+        <v>250000.89000000103</v>
       </c>
       <c r="J87">
-        <v>-0.014971891125567613</v>
+        <v>-0.013875047968675447</v>
       </c>
       <c r="K87">
-        <v>-0.01317095725949065</v>
+        <v>-0.011267506208370793</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>0.9963937401771545</v>
       </c>
       <c r="X87">
-        <v>0.9963925840393764</v>
+        <v>0.9963926396472824</v>
       </c>
       <c r="Y87">
         <v>0.9959000945091248</v>
@@ -8394,7 +8394,7 @@
         <v>125.02525170775829</v>
       </c>
       <c r="E88">
-        <v>125.92</v>
+        <v>126.0</v>
       </c>
       <c r="F88">
         <v>125.03</v>
@@ -8403,16 +8403,16 @@
         <v>239873.27515625</v>
       </c>
       <c r="H88">
-        <v>215024.95999999912</v>
+        <v>214220.71999999965</v>
       </c>
       <c r="I88">
-        <v>215211.58999999973</v>
+        <v>211919.01000000007</v>
       </c>
       <c r="J88">
-        <v>-0.10281130792993087</v>
+        <v>-0.11653763904311941</v>
       </c>
       <c r="K88">
-        <v>-0.10358934374854822</v>
+        <v>-0.10694211407894703</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>0.9988002479076385</v>
       </c>
       <c r="X88">
-        <v>0.998800210787849</v>
+        <v>0.998799509900909</v>
       </c>
       <c r="Y88">
         <v>0.9980553388595581</v>
@@ -8489,7 +8489,7 @@
         <v>143.79446984026313</v>
       </c>
       <c r="E89">
-        <v>144.43</v>
+        <v>144.46</v>
       </c>
       <c r="F89">
         <v>143.79</v>
@@ -8498,16 +8498,16 @@
         <v>303141.33521875</v>
       </c>
       <c r="H89">
-        <v>248665.33000000042</v>
+        <v>248495.4700000001</v>
       </c>
       <c r="I89">
-        <v>248542.34000000003</v>
+        <v>248846.28999999963</v>
       </c>
       <c r="J89">
-        <v>-0.18011069054423332</v>
+        <v>-0.17910802292788772</v>
       </c>
       <c r="K89">
-        <v>-0.17970497220195691</v>
+        <v>-0.18026530489257386</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>0.9975904822349548</v>
       </c>
       <c r="X89">
-        <v>0.9975900933593647</v>
+        <v>0.9975902004795137</v>
       </c>
       <c r="Y89">
         <v>0.9974526762962341</v>
@@ -8584,7 +8584,7 @@
         <v>139.47900079617625</v>
       </c>
       <c r="E90">
-        <v>140.9</v>
+        <v>140.98</v>
       </c>
       <c r="F90">
         <v>139.48</v>
@@ -8593,16 +8593,16 @@
         <v>294365.7165</v>
       </c>
       <c r="H90">
-        <v>242428.69999999966</v>
+        <v>242733.94999999937</v>
       </c>
       <c r="I90">
-        <v>241608.64999999967</v>
+        <v>241809.47999999963</v>
       </c>
       <c r="J90">
-        <v>-0.1792228630673447</v>
+        <v>-0.1785406164987299</v>
       </c>
       <c r="K90">
-        <v>-0.17643704272878638</v>
+        <v>-0.1754000673512556</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>0.9976650476455688</v>
       </c>
       <c r="X90">
-        <v>0.9976652357147698</v>
+        <v>0.9976652454836303</v>
       </c>
       <c r="Y90">
         <v>0.9976041913032532</v>
@@ -8679,7 +8679,7 @@
         <v>127.65413573463212</v>
       </c>
       <c r="E91">
-        <v>129.92</v>
+        <v>129.88</v>
       </c>
       <c r="F91">
         <v>127.65</v>
@@ -8688,16 +8688,16 @@
         <v>271317.988328125</v>
       </c>
       <c r="H91">
-        <v>216816.26999999976</v>
+        <v>216827.67999999993</v>
       </c>
       <c r="I91">
-        <v>217315.92999999961</v>
+        <v>217868.45999999988</v>
       </c>
       <c r="J91">
-        <v>-0.19903604129194952</v>
+        <v>-0.19699957477012037</v>
       </c>
       <c r="K91">
-        <v>-0.2008776442135943</v>
+        <v>-0.20083559023821845</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>0.9997003674507141</v>
       </c>
       <c r="X91">
-        <v>0.9997007628516347</v>
+        <v>0.9997008033603295</v>
       </c>
       <c r="Y91">
         <v>0.9995740056037903</v>
@@ -8774,7 +8774,7 @@
         <v>148.16769408835682</v>
       </c>
       <c r="E92">
-        <v>150.78</v>
+        <v>150.83</v>
       </c>
       <c r="F92">
         <v>148.17</v>
@@ -8783,16 +8783,16 @@
         <v>297078.172875</v>
       </c>
       <c r="H92">
-        <v>251721.9300000003</v>
+        <v>251795.78000000023</v>
       </c>
       <c r="I92">
-        <v>253511.39999999997</v>
+        <v>253392.14999999976</v>
       </c>
       <c r="J92">
-        <v>-0.1466508712281982</v>
+        <v>-0.14705228072538928</v>
       </c>
       <c r="K92">
-        <v>-0.15267443729056454</v>
+        <v>-0.15242584952228377</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>0.9955311417579651</v>
       </c>
       <c r="X92">
-        <v>0.9955531984136848</v>
+        <v>0.9955538534852091</v>
       </c>
       <c r="Y92">
         <v>0.9912654757499695</v>
@@ -8869,7 +8869,7 @@
         <v>136.3327818125497</v>
       </c>
       <c r="E93">
-        <v>139.35</v>
+        <v>139.33</v>
       </c>
       <c r="F93">
         <v>136.33</v>
@@ -8878,16 +8878,16 @@
         <v>255156.774578125</v>
       </c>
       <c r="H93">
-        <v>238170.25999999963</v>
+        <v>238519.10000000056</v>
       </c>
       <c r="I93">
-        <v>235609.24999999953</v>
+        <v>235584.76000000068</v>
       </c>
       <c r="J93">
-        <v>-0.07660985921477202</v>
+        <v>-0.07670583942160504</v>
       </c>
       <c r="K93">
-        <v>-0.06657285351804122</v>
+        <v>-0.06520569405077763</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>0.999089926481247</v>
       </c>
       <c r="X93">
-        <v>0.9990922451746629</v>
+        <v>0.9990922689550708</v>
       </c>
       <c r="Y93">
         <v>0.9983819723129272</v>
@@ -8964,7 +8964,7 @@
         <v>145.95654489301546</v>
       </c>
       <c r="E94">
-        <v>148.6</v>
+        <v>148.59</v>
       </c>
       <c r="F94">
         <v>145.96</v>
@@ -8973,16 +8973,16 @@
         <v>279587.954703125</v>
       </c>
       <c r="H94">
-        <v>253845.5799999994</v>
+        <v>254066.55</v>
       </c>
       <c r="I94">
-        <v>252566.2300000002</v>
+        <v>252854.7199999998</v>
       </c>
       <c r="J94">
-        <v>-0.0966483864865254</v>
+        <v>-0.09561654661235804</v>
       </c>
       <c r="K94">
-        <v>-0.0920725455803689</v>
+        <v>-0.09128220394982471</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>0.9989049136638641</v>
       </c>
       <c r="X94">
-        <v>0.998903294321914</v>
+        <v>0.9989040140792594</v>
       </c>
       <c r="Y94">
         <v>0.9981234669685364</v>
@@ -9059,7 +9059,7 @@
         <v>151.7642404553967</v>
       </c>
       <c r="E95">
-        <v>154.61</v>
+        <v>154.53</v>
       </c>
       <c r="F95">
         <v>151.76</v>
@@ -9068,16 +9068,16 @@
         <v>281901.59746875</v>
       </c>
       <c r="H95">
-        <v>263854.5399999994</v>
+        <v>263417.62000000064</v>
       </c>
       <c r="I95">
-        <v>262744.26000000024</v>
+        <v>263047.219999999</v>
       </c>
       <c r="J95">
-        <v>-0.06795753426290341</v>
+        <v>-0.06688283300998722</v>
       </c>
       <c r="K95">
-        <v>-0.064018996808811</v>
+        <v>-0.06556889934190038</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>0.9981271326541901</v>
       </c>
       <c r="X95">
-        <v>0.9981245090953345</v>
+        <v>0.9981251460330812</v>
       </c>
       <c r="Y95">
         <v>0.9963263869285583</v>
@@ -9163,16 +9163,16 @@
         <v>285099.384671875</v>
       </c>
       <c r="H96">
-        <v>237171.189999999</v>
+        <v>236032.63999999987</v>
       </c>
       <c r="I96">
-        <v>237325.20999999996</v>
+        <v>237232.42999999964</v>
       </c>
       <c r="J96">
-        <v>-0.16757024827275235</v>
+        <v>-0.16789567864892488</v>
       </c>
       <c r="K96">
-        <v>-0.1681104809364539</v>
+        <v>-0.1721040006043743</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -9243,16 +9243,16 @@
         <v>284502.900265625</v>
       </c>
       <c r="H97">
-        <v>233775.3000000003</v>
+        <v>232580.8999999991</v>
       </c>
       <c r="I97">
-        <v>233650.88000000012</v>
+        <v>233650.28000000035</v>
       </c>
       <c r="J97">
-        <v>-0.17873990113333493</v>
+        <v>-0.17874201007492818</v>
       </c>
       <c r="K97">
-        <v>-0.17830257694478002</v>
+        <v>-0.18250077667802023</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -9323,16 +9323,16 @@
         <v>301208.75803125</v>
       </c>
       <c r="H98">
-        <v>226479.34999999992</v>
+        <v>224751.5700000007</v>
       </c>
       <c r="I98">
-        <v>226477.84999999954</v>
+        <v>226916.2300000002</v>
       </c>
       <c r="J98">
-        <v>-0.24810337029940283</v>
+        <v>-0.2466479677312106</v>
       </c>
       <c r="K98">
-        <v>-0.2480983903645225</v>
+        <v>-0.2538345449547551</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>144.94475128156424</v>
       </c>
       <c r="E99">
-        <v>149.13</v>
+        <v>149.26</v>
       </c>
       <c r="F99">
         <v>144.94</v>
@@ -9403,16 +9403,16 @@
         <v>293231.314453125</v>
       </c>
       <c r="H99">
-        <v>249270.93000000037</v>
+        <v>249889.0099999999</v>
       </c>
       <c r="I99">
-        <v>249405.21000000005</v>
+        <v>249801.430000001</v>
       </c>
       <c r="J99">
-        <v>-0.14945915491618084</v>
+        <v>-0.14810793497318156</v>
       </c>
       <c r="K99">
-        <v>-0.14991708690836972</v>
+        <v>-0.14780926291572338</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>0.9527916610240936</v>
       </c>
       <c r="X99">
-        <v>0.9528218736558113</v>
+        <v>0.9528168775377295</v>
       </c>
       <c r="Y99">
         <v>0.9467945098876953</v>
@@ -9489,7 +9489,7 @@
         <v>136.6697014858601</v>
       </c>
       <c r="E100">
-        <v>138.68</v>
+        <v>138.59</v>
       </c>
       <c r="F100">
         <v>136.67</v>
@@ -9498,16 +9498,16 @@
         <v>281159.395875</v>
       </c>
       <c r="H100">
-        <v>232155.8799999998</v>
+        <v>231957.4099999997</v>
       </c>
       <c r="I100">
-        <v>232717.74000000028</v>
+        <v>232774.83000000002</v>
       </c>
       <c r="J100">
-        <v>-0.17229250235171323</v>
+        <v>-0.1720894502722262</v>
       </c>
       <c r="K100">
-        <v>-0.17429087056648304</v>
+        <v>-0.17499676908138925</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>0.9989614486694336</v>
       </c>
       <c r="X100">
-        <v>0.9989614523212579</v>
+        <v>0.9989614515395997</v>
       </c>
       <c r="Y100">
         <v>0.9989598989486694</v>
@@ -9584,7 +9584,7 @@
         <v>142.4767008628159</v>
       </c>
       <c r="E101">
-        <v>144.28</v>
+        <v>144.3</v>
       </c>
       <c r="F101">
         <v>142.48</v>
@@ -9593,16 +9593,16 @@
         <v>297878.272328125</v>
       </c>
       <c r="H101">
-        <v>244939.9400000003</v>
+        <v>245261.47000000012</v>
       </c>
       <c r="I101">
-        <v>245170.0700000002</v>
+        <v>245005.0700000002</v>
       </c>
       <c r="J101">
-        <v>-0.17694544122393924</v>
+        <v>-0.17749935876451853</v>
       </c>
       <c r="K101">
-        <v>-0.1777180051246269</v>
+        <v>-0.17663860447721866</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>0.9998702108860016</v>
       </c>
       <c r="X101">
-        <v>0.9998701287200971</v>
+        <v>0.9998701439967297</v>
       </c>
       <c r="Y101">
         <v>0.9997815489768982</v>
@@ -9679,7 +9679,7 @@
         <v>184.56669512538858</v>
       </c>
       <c r="E102">
-        <v>186.89</v>
+        <v>187.05</v>
       </c>
       <c r="F102">
         <v>176.59</v>
@@ -9688,16 +9688,16 @@
         <v>434819.7075</v>
       </c>
       <c r="H102">
-        <v>310095.25999999896</v>
+        <v>313438.20999999915</v>
       </c>
       <c r="I102">
-        <v>302026.71999999986</v>
+        <v>300963.89000000036</v>
       </c>
       <c r="J102">
-        <v>-0.3053978124945042</v>
+        <v>-0.30784211292906877</v>
       </c>
       <c r="K102">
-        <v>-0.28684175383196275</v>
+        <v>-0.27915362483886696</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>0.9995952248573303</v>
       </c>
       <c r="X102">
-        <v>0.9995855416403928</v>
+        <v>0.9995856445297169</v>
       </c>
       <c r="Y102">
         <v>0.9993669390678406</v>
@@ -9783,16 +9783,16 @@
         <v>333947.65609375003</v>
       </c>
       <c r="H103">
-        <v>275762.9400000003</v>
+        <v>270206.3600000004</v>
       </c>
       <c r="I103">
-        <v>279429.1100000005</v>
+        <v>276234.96000000014</v>
       </c>
       <c r="J103">
-        <v>-0.16325476492772384</v>
+        <v>-0.17281958726354424</v>
       </c>
       <c r="K103">
-        <v>-0.17423304231072484</v>
+        <v>-0.190872117023799</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>148.79339513769824</v>
       </c>
       <c r="E104">
-        <v>152.32</v>
+        <v>152.25</v>
       </c>
       <c r="F104">
         <v>148.79</v>
@@ -9863,16 +9863,16 @@
         <v>298827.34815625</v>
       </c>
       <c r="H104">
-        <v>256657.65999999968</v>
+        <v>255218.68000000084</v>
       </c>
       <c r="I104">
-        <v>257003.1200000005</v>
+        <v>256828.75999999986</v>
       </c>
       <c r="J104">
-        <v>-0.13996117963868754</v>
+        <v>-0.14054466037121224</v>
       </c>
       <c r="K104">
-        <v>-0.1411172317943295</v>
+        <v>-0.14593265450874063</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>0.9988217353820801</v>
       </c>
       <c r="X104">
-        <v>0.9988263391732354</v>
+        <v>0.9988262941308388</v>
       </c>
       <c r="Y104">
         <v>0.9983519315719604</v>
@@ -9958,16 +9958,16 @@
         <v>294353.7740625</v>
       </c>
       <c r="H105">
-        <v>255934.35000000003</v>
+        <v>250201.67999999927</v>
       </c>
       <c r="I105">
-        <v>256677.96000000034</v>
+        <v>256922.19</v>
       </c>
       <c r="J105">
-        <v>-0.12799500934715366</v>
+        <v>-0.12716529346945676</v>
       </c>
       <c r="K105">
-        <v>-0.13052125519662056</v>
+        <v>-0.14999669769182553</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>158.15660949467693</v>
       </c>
       <c r="E106">
-        <v>159.91</v>
+        <v>159.87</v>
       </c>
       <c r="F106">
         <v>158.16</v>
@@ -10038,16 +10038,16 @@
         <v>373883.9655625</v>
       </c>
       <c r="H106">
-        <v>274666.68000000005</v>
+        <v>271497.6799999999</v>
       </c>
       <c r="I106">
-        <v>273213.6399999999</v>
+        <v>273885.90999999945</v>
       </c>
       <c r="J106">
-        <v>-0.2692555306859546</v>
+        <v>-0.267457459460867</v>
       </c>
       <c r="K106">
-        <v>-0.26536919124956265</v>
+        <v>-0.27384508294829457</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>0.9999380707740784</v>
       </c>
       <c r="X106">
-        <v>0.9999383317072259</v>
+        <v>0.9999383370149145</v>
       </c>
       <c r="Y106">
         <v>0.9999287128448486</v>
@@ -10124,7 +10124,7 @@
         <v>106.01779832005539</v>
       </c>
       <c r="E107">
-        <v>107.31</v>
+        <v>107.38</v>
       </c>
       <c r="F107">
         <v>106.02</v>
@@ -10133,16 +10133,16 @@
         <v>215238.83434375</v>
       </c>
       <c r="H107">
-        <v>184328.86999999982</v>
+        <v>184470.01000000004</v>
       </c>
       <c r="I107">
-        <v>183445.22999999952</v>
+        <v>183342.61000000028</v>
       </c>
       <c r="J107">
-        <v>-0.1477131412678722</v>
+        <v>-0.14818991396696304</v>
       </c>
       <c r="K107">
-        <v>-0.1436077482857253</v>
+        <v>-0.14295201159940407</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>0.9901601076126099</v>
       </c>
       <c r="X107">
-        <v>0.9901120687598649</v>
+        <v>0.9901046117255418</v>
       </c>
       <c r="Y107">
         <v>0.9806849956512451</v>
@@ -10219,7 +10219,7 @@
         <v>159.89690855474794</v>
       </c>
       <c r="E108">
-        <v>161.09</v>
+        <v>161.04</v>
       </c>
       <c r="F108">
         <v>144.02</v>
@@ -10228,16 +10228,16 @@
         <v>383348.8025</v>
       </c>
       <c r="H108">
-        <v>277347.45000000036</v>
+        <v>274872.53999999934</v>
       </c>
       <c r="I108">
-        <v>249144.0799999997</v>
+        <v>249147.0900000001</v>
       </c>
       <c r="J108">
-        <v>-0.3500851486291008</v>
+        <v>-0.3500772967720432</v>
       </c>
       <c r="K108">
-        <v>-0.27651410884477623</v>
+        <v>-0.2829701352725646</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>0.998537003993988</v>
       </c>
       <c r="X108">
-        <v>0.9985370165235055</v>
+        <v>0.9985371076599395</v>
       </c>
       <c r="Y108">
         <v>0.9971742630004883</v>
@@ -10314,7 +10314,7 @@
         <v>149.37739021202708</v>
       </c>
       <c r="E109">
-        <v>152.11</v>
+        <v>151.93</v>
       </c>
       <c r="F109">
         <v>149.37</v>
@@ -10323,16 +10323,16 @@
         <v>318861.58053125</v>
       </c>
       <c r="H109">
-        <v>259587.57000000012</v>
+        <v>258990.50999999946</v>
       </c>
       <c r="I109">
-        <v>258108.41</v>
+        <v>257304.42999999967</v>
       </c>
       <c r="J109">
-        <v>-0.19053148526087757</v>
+        <v>-0.1930528928216782</v>
       </c>
       <c r="K109">
-        <v>-0.1858926071698397</v>
+        <v>-0.18776508110980425</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>0.9741301834583282</v>
       </c>
       <c r="X109">
-        <v>0.97413078073367</v>
+        <v>0.9741321876730804</v>
       </c>
       <c r="Y109">
         <v>0.9719126224517822</v>
@@ -10409,7 +10409,7 @@
         <v>161.87688584509854</v>
       </c>
       <c r="E110">
-        <v>162.5</v>
+        <v>162.44</v>
       </c>
       <c r="F110">
         <v>161.84</v>
@@ -10418,16 +10418,16 @@
         <v>364927.05753125</v>
       </c>
       <c r="H110">
-        <v>276994.7600000004</v>
+        <v>277112.06999999954</v>
       </c>
       <c r="I110">
-        <v>285271.09000000014</v>
+        <v>274438.5300000007</v>
       </c>
       <c r="J110">
-        <v>-0.21827914890752828</v>
+        <v>-0.24796332763979942</v>
       </c>
       <c r="K110">
-        <v>-0.24095855792693482</v>
+        <v>-0.2406370964250316</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>0.9976194798946381</v>
       </c>
       <c r="X110">
-        <v>0.9976147147229153</v>
+        <v>0.9976154395111151</v>
       </c>
       <c r="Y110">
         <v>0.9965003728866577</v>
@@ -10504,7 +10504,7 @@
         <v>368.7150641456625</v>
       </c>
       <c r="E111">
-        <v>371.04</v>
+        <v>370.68</v>
       </c>
       <c r="F111">
         <v>368.8</v>
@@ -10513,16 +10513,16 @@
         <v>773574.863265625</v>
       </c>
       <c r="H111">
-        <v>623852.089999999</v>
+        <v>621065.9699999983</v>
       </c>
       <c r="I111">
-        <v>623015.609999999</v>
+        <v>620932.6600000008</v>
       </c>
       <c r="J111">
-        <v>-0.19462790276049582</v>
+        <v>-0.19732053161765012</v>
       </c>
       <c r="K111">
-        <v>-0.1935465853085962</v>
+        <v>-0.1971482018195557</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>0.9962311685085297</v>
       </c>
       <c r="X111">
-        <v>0.9963043172645112</v>
+        <v>0.9963033242203367</v>
       </c>
       <c r="Y111">
         <v>0.9940998554229736</v>
@@ -10599,7 +10599,7 @@
         <v>140.62422175360035</v>
       </c>
       <c r="E112">
-        <v>143.55</v>
+        <v>143.58</v>
       </c>
       <c r="F112">
         <v>140.63</v>
@@ -10608,16 +10608,16 @@
         <v>296462.46203125</v>
       </c>
       <c r="H112">
-        <v>243561.43999999942</v>
+        <v>243747.42999999973</v>
       </c>
       <c r="I112">
-        <v>243140.69000000053</v>
+        <v>242515.4500000002</v>
       </c>
       <c r="J112">
-        <v>-0.17986011337121274</v>
+        <v>-0.18196911562302037</v>
       </c>
       <c r="K112">
-        <v>-0.1784408780416669</v>
+        <v>-0.17781351362350084</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>0.9907946288585663</v>
       </c>
       <c r="X112">
-        <v>0.9907760149325182</v>
+        <v>0.9907792178392543</v>
       </c>
       <c r="Y112">
         <v>0.9854668378829956</v>
@@ -10694,7 +10694,7 @@
         <v>118.77514134674254</v>
       </c>
       <c r="E113">
-        <v>122.22</v>
+        <v>122.21</v>
       </c>
       <c r="F113">
         <v>118.78</v>
@@ -10703,16 +10703,16 @@
         <v>274320.081625</v>
       </c>
       <c r="H113">
-        <v>203962.20999999993</v>
+        <v>204171.70000000036</v>
       </c>
       <c r="I113">
-        <v>200711.18000000052</v>
+        <v>201024.08000000013</v>
       </c>
       <c r="J113">
-        <v>-0.26833216580047553</v>
+        <v>-0.26719152746971214</v>
       </c>
       <c r="K113">
-        <v>-0.25648093718920806</v>
+        <v>-0.2557172672502103</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>0.9962071776390076</v>
       </c>
       <c r="X113">
-        <v>0.9962324498335124</v>
+        <v>0.9962319661711676</v>
       </c>
       <c r="Y113">
         <v>0.9937394857406616</v>
@@ -10789,7 +10789,7 @@
         <v>268.76302286252576</v>
       </c>
       <c r="E114">
-        <v>272.25</v>
+        <v>272.28</v>
       </c>
       <c r="F114">
         <v>268.76</v>
@@ -10798,16 +10798,16 @@
         <v>553058.4800625</v>
       </c>
       <c r="H114">
-        <v>462616.3399999997</v>
+        <v>462893.37000000046</v>
       </c>
       <c r="I114">
-        <v>459330.5600000008</v>
+        <v>459298.0599999992</v>
       </c>
       <c r="J114">
-        <v>-0.16947198793861218</v>
+        <v>-0.16953075206785573</v>
       </c>
       <c r="K114">
-        <v>-0.16353088022857842</v>
+        <v>-0.16302997479093018</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>0.9980089962482452</v>
       </c>
       <c r="X114">
-        <v>0.99799948111842</v>
+        <v>0.997999520191674</v>
       </c>
       <c r="Y114">
         <v>0.9969768524169922</v>
@@ -10884,7 +10884,7 @@
         <v>259.62690924304076</v>
       </c>
       <c r="E115">
-        <v>263.34</v>
+        <v>263.26</v>
       </c>
       <c r="F115">
         <v>259.63</v>
@@ -10893,16 +10893,16 @@
         <v>587998.245796875</v>
       </c>
       <c r="H115">
-        <v>448316.02999999846</v>
+        <v>448000.4800000004</v>
       </c>
       <c r="I115">
-        <v>448762.8399999983</v>
+        <v>448877.31000000046</v>
       </c>
       <c r="J115">
-        <v>-0.23679561425932522</v>
+        <v>-0.23660093680778443</v>
       </c>
       <c r="K115">
-        <v>-0.23755549747869484</v>
+        <v>-0.23809214873956794</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>0.9980018734931946</v>
       </c>
       <c r="X115">
-        <v>0.9980019483013479</v>
+        <v>0.9980024293243104</v>
       </c>
       <c r="Y115">
         <v>0.996044397354126</v>
@@ -10979,7 +10979,7 @@
         <v>253.7518753339819</v>
       </c>
       <c r="E116">
-        <v>257.21</v>
+        <v>257.09</v>
       </c>
       <c r="F116">
         <v>253.75</v>
@@ -10988,16 +10988,16 @@
         <v>564582.27475</v>
       </c>
       <c r="H116">
-        <v>441822.38000000117</v>
+        <v>441102.7100000007</v>
       </c>
       <c r="I116">
-        <v>439942.5099999995</v>
+        <v>440090.4200000002</v>
       </c>
       <c r="J116">
-        <v>-0.2207645728962916</v>
+        <v>-0.22050259159327207</v>
       </c>
       <c r="K116">
-        <v>-0.21743490761263723</v>
+        <v>-0.21870960225358946</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>0.9994970262050629</v>
       </c>
       <c r="X116">
-        <v>0.999497192120275</v>
+        <v>0.9994971796760683</v>
       </c>
       <c r="Y116">
         <v>0.9992140531539917</v>
@@ -11074,7 +11074,7 @@
         <v>281.0051166684575</v>
       </c>
       <c r="E117">
-        <v>141.99</v>
+        <v>281.4</v>
       </c>
       <c r="F117">
         <v>281.01</v>
@@ -11083,16 +11083,16 @@
         <v>591670.0456953126</v>
       </c>
       <c r="H117">
-        <v>245617.06999999975</v>
+        <v>469772.85999999807</v>
       </c>
       <c r="I117">
-        <v>487203.7599999996</v>
+        <v>487072.67999999935</v>
       </c>
       <c r="J117">
-        <v>-0.17656172803635406</v>
+        <v>-0.17678327043309008</v>
       </c>
       <c r="K117">
-        <v>-0.5848749285400141</v>
+        <v>-0.2060222358427232</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -11134,16 +11134,16 @@
         <v>8760</v>
       </c>
       <c r="V117">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W117">
-        <v>0.9997032880783081</v>
+        <v>0.8630735874176025</v>
       </c>
       <c r="X117">
-        <v>0.9997024686121101</v>
+        <v>0.7946611777628205</v>
       </c>
       <c r="Y117">
-        <v>0.9995418787002563</v>
+        <v>0.5898141860961914</v>
       </c>
       <c r="Z117">
         <v>0.9998646974563599</v>
@@ -11169,7 +11169,7 @@
         <v>264.4266547880194</v>
       </c>
       <c r="E118">
-        <v>268.18</v>
+        <v>268.28</v>
       </c>
       <c r="F118">
         <v>264.43</v>
@@ -11178,16 +11178,16 @@
         <v>589804.873</v>
       </c>
       <c r="H118">
-        <v>364951.60000000044</v>
+        <v>356439.4399999999</v>
       </c>
       <c r="I118">
-        <v>366566.1299999987</v>
+        <v>358114.84999999986</v>
       </c>
       <c r="J118">
-        <v>-0.37849592843225166</v>
+        <v>-0.39282487074331135</v>
       </c>
       <c r="K118">
-        <v>-0.38123332527976517</v>
+        <v>-0.39566548816900016</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>0.9998101890087128</v>
       </c>
       <c r="X118">
-        <v>0.9998096843019486</v>
+        <v>0.99980972136729</v>
       </c>
       <c r="Y118">
         <v>0.9997469782829285</v>
@@ -11264,7 +11264,7 @@
         <v>169.59765640637158</v>
       </c>
       <c r="E119">
-        <v>170.7</v>
+        <v>170.76</v>
       </c>
       <c r="F119">
         <v>169.62</v>
@@ -11273,16 +11273,16 @@
         <v>383475.52278125</v>
       </c>
       <c r="H119">
-        <v>291072.1199999999</v>
+        <v>290155.900000001</v>
       </c>
       <c r="I119">
-        <v>291320.3000000004</v>
+        <v>287763.37000000046</v>
       </c>
       <c r="J119">
-        <v>-0.24031578890060915</v>
+        <v>-0.24959129617210965</v>
       </c>
       <c r="K119">
-        <v>-0.24096297492750476</v>
+        <v>-0.24335222781476537</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>0.9961581826210022</v>
       </c>
       <c r="X119">
-        <v>0.9961579898195684</v>
+        <v>0.9961579535321131</v>
       </c>
       <c r="Y119">
         <v>0.9958497285842896</v>
@@ -11359,7 +11359,7 @@
         <v>180.09436292188286</v>
       </c>
       <c r="E120">
-        <v>181.16</v>
+        <v>181.06</v>
       </c>
       <c r="F120">
         <v>180.09</v>
@@ -11368,16 +11368,16 @@
         <v>407240.082125</v>
       </c>
       <c r="H120">
-        <v>310846.38000000035</v>
+        <v>308222.37000000075</v>
       </c>
       <c r="I120">
-        <v>310140.02999999915</v>
+        <v>306943.6899999993</v>
       </c>
       <c r="J120">
-        <v>-0.23843441838614637</v>
+        <v>-0.24628320375943571</v>
       </c>
       <c r="K120">
-        <v>-0.23669993784013668</v>
+        <v>-0.24314333601034474</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>0.9962729513645172</v>
       </c>
       <c r="X120">
-        <v>0.9962732729227672</v>
+        <v>0.9962715776756855</v>
       </c>
       <c r="Y120">
         <v>0.9942824840545654</v>
@@ -11454,7 +11454,7 @@
         <v>170.34766711331602</v>
       </c>
       <c r="E121">
-        <v>171.21</v>
+        <v>171.09</v>
       </c>
       <c r="F121">
         <v>170.35</v>
@@ -11463,16 +11463,16 @@
         <v>321424.722390625</v>
       </c>
       <c r="H121">
-        <v>293592.36000000057</v>
+        <v>292246.95000000054</v>
       </c>
       <c r="I121">
-        <v>297081.77999999997</v>
+        <v>289743.5900000002</v>
       </c>
       <c r="J121">
-        <v>-0.07573450545301001</v>
+        <v>-0.09856470328415792</v>
       </c>
       <c r="K121">
-        <v>-0.08659060878584181</v>
+        <v>-0.09077637890953805</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>0.9918288886547089</v>
       </c>
       <c r="X121">
-        <v>0.9918292507828163</v>
+        <v>0.9918265134135541</v>
       </c>
       <c r="Y121">
         <v>0.9863615036010742</v>
@@ -11549,7 +11549,7 @@
         <v>182.5233219353056</v>
       </c>
       <c r="E122">
-        <v>184.47</v>
+        <v>184.55</v>
       </c>
       <c r="F122">
         <v>182.55</v>
@@ -11558,16 +11558,16 @@
         <v>390800.9315</v>
       </c>
       <c r="H122">
-        <v>319917.9800000006</v>
+        <v>319049.7299999997</v>
       </c>
       <c r="I122">
-        <v>316671.4599999999</v>
+        <v>316778.36999999924</v>
       </c>
       <c r="J122">
-        <v>-0.1896860153722538</v>
+        <v>-0.1894124489823555</v>
       </c>
       <c r="K122">
-        <v>-0.18137866567495473</v>
+        <v>-0.1836003850466777</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>0.9655132591724396</v>
       </c>
       <c r="X122">
-        <v>0.9655324932533587</v>
+        <v>0.9655235352964522</v>
       </c>
       <c r="Y122">
         <v>0.9319942593574524</v>
@@ -11644,7 +11644,7 @@
         <v>185.03040390393028</v>
       </c>
       <c r="E123">
-        <v>186.45</v>
+        <v>186.29</v>
       </c>
       <c r="F123">
         <v>185.03</v>
@@ -11653,16 +11653,16 @@
         <v>396697.652375</v>
       </c>
       <c r="H123">
-        <v>274019.4400000003</v>
+        <v>264580.83000000066</v>
       </c>
       <c r="I123">
-        <v>257345.62999999966</v>
+        <v>257762.32000000007</v>
       </c>
       <c r="J123">
-        <v>-0.3512801791004054</v>
+        <v>-0.35022978216080736</v>
       </c>
       <c r="K123">
-        <v>-0.3092486472771749</v>
+        <v>-0.3330416038109264</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>0.9931499063968658</v>
       </c>
       <c r="X123">
-        <v>0.9931485599153043</v>
+        <v>0.9931489293100908</v>
       </c>
       <c r="Y123">
         <v>0.988623857498169</v>
@@ -11739,7 +11739,7 @@
         <v>186.27467386796042</v>
       </c>
       <c r="E124">
-        <v>187.3</v>
+        <v>187.33</v>
       </c>
       <c r="F124">
         <v>186.27</v>
@@ -11748,16 +11748,16 @@
         <v>359206.05378125</v>
       </c>
       <c r="H124">
-        <v>322216.1200000011</v>
+        <v>319713.46</v>
       </c>
       <c r="I124">
-        <v>321489.22</v>
+        <v>319228.2900000001</v>
       </c>
       <c r="J124">
-        <v>-0.10500055158930846</v>
+        <v>-0.11129479406156018</v>
       </c>
       <c r="K124">
-        <v>-0.10297692199746479</v>
+        <v>-0.10994412083405554</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>0.9968272149562836</v>
       </c>
       <c r="X124">
-        <v>0.9968259518625942</v>
+        <v>0.9968262930388343</v>
       </c>
       <c r="Y124">
         <v>0.9938325881958008</v>
@@ -11834,7 +11834,7 @@
         <v>117.5404949879979</v>
       </c>
       <c r="E125">
-        <v>119.51</v>
+        <v>119.5</v>
       </c>
       <c r="F125">
         <v>117.54</v>
@@ -11843,16 +11843,16 @@
         <v>267685.017</v>
       </c>
       <c r="H125">
-        <v>202466.49999999994</v>
+        <v>201382.76999999967</v>
       </c>
       <c r="I125">
-        <v>201365.52</v>
+        <v>201357.88999999937</v>
       </c>
       <c r="J125">
-        <v>-0.24775199502480935</v>
+        <v>-0.2477804986746816</v>
       </c>
       <c r="K125">
-        <v>-0.24363902668485943</v>
+        <v>-0.2476875536145541</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>0.9919279217720032</v>
       </c>
       <c r="X125">
-        <v>0.9918793031224902</v>
+        <v>0.9918795513994345</v>
       </c>
       <c r="Y125">
         <v>0.9876033663749695</v>
@@ -11929,7 +11929,7 @@
         <v>177.91641275282072</v>
       </c>
       <c r="E126">
-        <v>178.55</v>
+        <v>178.49</v>
       </c>
       <c r="F126">
         <v>177.9</v>
@@ -11938,16 +11938,16 @@
         <v>410368.4088125</v>
       </c>
       <c r="H126">
-        <v>302446.39999999845</v>
+        <v>302610.4200000003</v>
       </c>
       <c r="I126">
-        <v>302051.5600000001</v>
+        <v>306251.61999999936</v>
       </c>
       <c r="J126">
-        <v>-0.26395026148806344</v>
+        <v>-0.2537154093166862</v>
       </c>
       <c r="K126">
-        <v>-0.26298810165431574</v>
+        <v>-0.2625884120181753</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>0.9954473674297333</v>
       </c>
       <c r="X126">
-        <v>0.995417997243837</v>
+        <v>0.9954191480337539</v>
       </c>
       <c r="Y126">
         <v>0.9930832386016846</v>
@@ -12024,7 +12024,7 @@
         <v>172.5386587912594</v>
       </c>
       <c r="E127">
-        <v>174.8</v>
+        <v>174.88</v>
       </c>
       <c r="F127">
         <v>172.54</v>
@@ -12033,16 +12033,16 @@
         <v>390191.9704375</v>
       </c>
       <c r="H127">
-        <v>296651.2999999992</v>
+        <v>296201.1099999998</v>
       </c>
       <c r="I127">
-        <v>295537.8599999997</v>
+        <v>296180.8299999997</v>
       </c>
       <c r="J127">
-        <v>-0.24258343997025372</v>
+        <v>-0.2409356100590459</v>
       </c>
       <c r="K127">
-        <v>-0.23972987022931044</v>
+        <v>-0.240883635642511</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>0.9867782890796661</v>
       </c>
       <c r="X127">
-        <v>0.9867784650243769</v>
+        <v>0.9867784732892493</v>
       </c>
       <c r="Y127">
         <v>0.9867442846298218</v>
@@ -12119,7 +12119,7 @@
         <v>180.95012060846994</v>
       </c>
       <c r="E128">
-        <v>183.04</v>
+        <v>183.1</v>
       </c>
       <c r="F128">
         <v>180.95</v>
@@ -12128,16 +12128,16 @@
         <v>344118.66585937503</v>
       </c>
       <c r="H128">
-        <v>312195.6299999993</v>
+        <v>311908.3100000002</v>
       </c>
       <c r="I128">
-        <v>318212.06999999855</v>
+        <v>306072.4799999996</v>
       </c>
       <c r="J128">
-        <v>-0.07528390183275695</v>
+        <v>-0.11056123841571305</v>
       </c>
       <c r="K128">
-        <v>-0.09276752186532408</v>
+        <v>-0.0936024664019176</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>0.9984196126461029</v>
       </c>
       <c r="X128">
-        <v>0.9984212641477511</v>
+        <v>0.9984211949673893</v>
       </c>
       <c r="Y128">
         <v>0.9973134398460388</v>
@@ -12214,7 +12214,7 @@
         <v>136.69953952973822</v>
       </c>
       <c r="E129">
-        <v>138.34</v>
+        <v>138.32</v>
       </c>
       <c r="F129">
         <v>137.09</v>
@@ -12223,16 +12223,16 @@
         <v>268456.8248125</v>
       </c>
       <c r="H129">
-        <v>238119.0699999993</v>
+        <v>237999.84999999957</v>
       </c>
       <c r="I129">
-        <v>236949.09999999992</v>
+        <v>237235.84000000003</v>
       </c>
       <c r="J129">
-        <v>-0.11736607864041529</v>
+        <v>-0.11629797392674159</v>
       </c>
       <c r="K129">
-        <v>-0.11300794767907155</v>
+        <v>-0.11345204143635637</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>0.992162436246872</v>
       </c>
       <c r="X129">
-        <v>0.992046994479921</v>
+        <v>0.9920466703786149</v>
       </c>
       <c r="Y129">
         <v>0.9880061745643616</v>
@@ -12309,7 +12309,7 @@
         <v>177.44237750926212</v>
       </c>
       <c r="E130">
-        <v>178.95</v>
+        <v>178.99</v>
       </c>
       <c r="F130">
         <v>177.45</v>
@@ -12318,16 +12318,16 @@
         <v>382171.0251875</v>
       </c>
       <c r="H130">
-        <v>307841.86999999924</v>
+        <v>306233.7100000019</v>
       </c>
       <c r="I130">
-        <v>306056.9200000004</v>
+        <v>304859.73000000056</v>
       </c>
       <c r="J130">
-        <v>-0.19916241727157796</v>
+        <v>-0.20229502000987415</v>
       </c>
       <c r="K130">
-        <v>-0.1944918643453766</v>
+        <v>-0.19869982333234681</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>0.9966250956058502</v>
       </c>
       <c r="X130">
-        <v>0.9966317464317015</v>
+        <v>0.9966325089691741</v>
       </c>
       <c r="Y130">
         <v>0.994657039642334</v>
@@ -12404,7 +12404,7 @@
         <v>180.2927807072308</v>
       </c>
       <c r="E131">
-        <v>182.19</v>
+        <v>182.26</v>
       </c>
       <c r="F131">
         <v>180.29</v>
@@ -12413,16 +12413,16 @@
         <v>387616.818625</v>
       </c>
       <c r="H131">
-        <v>312335.3499999992</v>
+        <v>310613.1499999999</v>
       </c>
       <c r="I131">
-        <v>309701.92999999976</v>
+        <v>300703.0900000006</v>
       </c>
       <c r="J131">
-        <v>-0.20101008233179643</v>
+        <v>-0.2242258964234576</v>
       </c>
       <c r="K131">
-        <v>-0.19421620788295016</v>
+        <v>-0.19865925554560965</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>0.9977696239948273</v>
       </c>
       <c r="X131">
-        <v>0.9977691678829722</v>
+        <v>0.9977692574212879</v>
       </c>
       <c r="Y131">
         <v>0.9969311952590942</v>
@@ -12508,16 +12508,16 @@
         <v>335165.876375</v>
       </c>
       <c r="H132">
-        <v>306792.2600000004</v>
+        <v>306147.6000000003</v>
       </c>
       <c r="I132">
-        <v>303992.22000000015</v>
+        <v>297678.64999999973</v>
       </c>
       <c r="J132">
-        <v>-0.09300963663771437</v>
+        <v>-0.1118467869714091</v>
       </c>
       <c r="K132">
-        <v>-0.0846554448856058</v>
+        <v>-0.0865788507137063</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>0.9930222034454346</v>
       </c>
       <c r="X132">
-        <v>0.9930258016747857</v>
+        <v>0.9930228687067012</v>
       </c>
       <c r="Y132">
         <v>0.986365556716919</v>
@@ -12594,7 +12594,7 @@
         <v>142.77089203090168</v>
       </c>
       <c r="E133">
-        <v>144.52</v>
+        <v>144.59</v>
       </c>
       <c r="F133">
         <v>142.77</v>
@@ -12603,16 +12603,16 @@
         <v>257397.78628125</v>
       </c>
       <c r="H133">
-        <v>247163.01999999917</v>
+        <v>247270.14000000025</v>
       </c>
       <c r="I133">
-        <v>246878.75000000026</v>
+        <v>247201.88999999917</v>
       </c>
       <c r="J133">
-        <v>-0.04086684828655032</v>
+        <v>-0.03961143733423613</v>
       </c>
       <c r="K133">
-        <v>-0.03976244873399046</v>
+        <v>-0.03934628353867667</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>0.987189382314682</v>
       </c>
       <c r="X133">
-        <v>0.9871618885862657</v>
+        <v>0.9871653804631453</v>
       </c>
       <c r="Y133">
         <v>0.9773149490356445</v>
@@ -12689,7 +12689,7 @@
         <v>150.53566437004977</v>
       </c>
       <c r="E134">
-        <v>152.76</v>
+        <v>152.82</v>
       </c>
       <c r="F134">
         <v>150.54</v>
@@ -12698,16 +12698,16 @@
         <v>264161.807515625</v>
       </c>
       <c r="H134">
-        <v>260230.16000000006</v>
+        <v>259655.05000000037</v>
       </c>
       <c r="I134">
-        <v>260413.68999999927</v>
+        <v>257694.81999999977</v>
       </c>
       <c r="J134">
-        <v>-0.014188718463413956</v>
+        <v>-0.024481160151218054</v>
       </c>
       <c r="K134">
-        <v>-0.014883482031718043</v>
+        <v>-0.017060594633302877</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>0.9982509911060333</v>
       </c>
       <c r="X134">
-        <v>0.9982521496482384</v>
+        <v>0.998251530739561</v>
       </c>
       <c r="Y134">
         <v>0.9977097511291504</v>
@@ -12784,7 +12784,7 @@
         <v>136.5281056747924</v>
       </c>
       <c r="E135">
-        <v>137.9</v>
+        <v>137.94</v>
       </c>
       <c r="F135">
         <v>136.48</v>
@@ -12793,16 +12793,16 @@
         <v>299422.51406250003</v>
       </c>
       <c r="H135">
-        <v>238158.88000000067</v>
+        <v>236830.1900000005</v>
       </c>
       <c r="I135">
-        <v>235824.8499999999</v>
+        <v>235628.61000000048</v>
       </c>
       <c r="J135">
-        <v>-0.21240107565600452</v>
+        <v>-0.21305647059386962</v>
       </c>
       <c r="K135">
-        <v>-0.20460597044386408</v>
+        <v>-0.20904347910669907</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>0.9975029230117798</v>
       </c>
       <c r="X135">
-        <v>0.9975039726818469</v>
+        <v>0.9975038724369009</v>
       </c>
       <c r="Y135">
         <v>0.996837854385376</v>
@@ -12888,16 +12888,16 @@
         <v>371543.1326875</v>
       </c>
       <c r="H136">
-        <v>302125.16</v>
+        <v>300317.37000000087</v>
       </c>
       <c r="I136">
-        <v>298489.019999999</v>
+        <v>298747.86000000034</v>
       </c>
       <c r="J136">
-        <v>-0.19662350413820137</v>
+        <v>-0.1959268420894938</v>
       </c>
       <c r="K136">
-        <v>-0.18683691496428906</v>
+        <v>-0.19170254116204097</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>0.9907559156417847</v>
       </c>
       <c r="X136">
-        <v>0.9907586296690652</v>
+        <v>0.9907599970550273</v>
       </c>
       <c r="Y136">
         <v>0.9823436737060547</v>
@@ -12974,7 +12974,7 @@
         <v>172.97653110219045</v>
       </c>
       <c r="E137">
-        <v>174.06</v>
+        <v>174.04</v>
       </c>
       <c r="F137">
         <v>172.98</v>
@@ -12983,16 +12983,16 @@
         <v>366785.9440625</v>
       </c>
       <c r="H137">
-        <v>299521.12000000046</v>
+        <v>297189.3000000006</v>
       </c>
       <c r="I137">
-        <v>297464.6700000003</v>
+        <v>300857.4600000006</v>
       </c>
       <c r="J137">
-        <v>-0.18899653922040008</v>
+        <v>-0.17974648464518386</v>
       </c>
       <c r="K137">
-        <v>-0.1833898630832966</v>
+        <v>-0.18974730408600443</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>0.9948228001594543</v>
       </c>
       <c r="X137">
-        <v>0.9948153622610406</v>
+        <v>0.994815841678825</v>
       </c>
       <c r="Y137">
         <v>0.9934305548667908</v>
@@ -13078,16 +13078,16 @@
         <v>343684.709640625</v>
       </c>
       <c r="H138">
-        <v>303529.8799999997</v>
+        <v>301045.6499999993</v>
       </c>
       <c r="I138">
-        <v>307346.8500000012</v>
+        <v>304022.66000000085</v>
       </c>
       <c r="J138">
-        <v>-0.10573021906799575</v>
+        <v>-0.11540242707363063</v>
       </c>
       <c r="K138">
-        <v>-0.11683624122415368</v>
+        <v>-0.12406446503020555</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>0.9956582486629486</v>
       </c>
       <c r="X138">
-        <v>0.9956564133195634</v>
+        <v>0.9956561569277574</v>
       </c>
       <c r="Y138">
         <v>0.9930731654167175</v>
@@ -13173,16 +13173,16 @@
         <v>191807.0495625</v>
       </c>
       <c r="H139">
-        <v>158335.36000000022</v>
+        <v>157674.42000000007</v>
       </c>
       <c r="I139">
-        <v>156957.04999999996</v>
+        <v>156452.5300000002</v>
       </c>
       <c r="J139">
-        <v>-0.18169300681070238</v>
+        <v>-0.18432335851649492</v>
       </c>
       <c r="K139">
-        <v>-0.17450708740292203</v>
+        <v>-0.17795294615267973</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>0.9979276061058044</v>
       </c>
       <c r="X139">
-        <v>0.9979297359680721</v>
+        <v>0.9979299355283</v>
       </c>
       <c r="Y139">
         <v>0.9963757395744324</v>
@@ -13259,7 +13259,7 @@
         <v>185.99539035435222</v>
       </c>
       <c r="E140">
-        <v>187.21</v>
+        <v>187.31</v>
       </c>
       <c r="F140">
         <v>185.94</v>
@@ -13268,16 +13268,16 @@
         <v>402560.2909375</v>
       </c>
       <c r="H140">
-        <v>321472.73000000016</v>
+        <v>321169.4700000007</v>
       </c>
       <c r="I140">
-        <v>321681.2600000008</v>
+        <v>321660.93000000075</v>
       </c>
       <c r="J140">
-        <v>-0.20091159699120986</v>
+        <v>-0.20096209874326476</v>
       </c>
       <c r="K140">
-        <v>-0.20142960635451548</v>
+        <v>-0.2021829345064134</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>0.996377170085907</v>
       </c>
       <c r="X140">
-        <v>0.9963745852913507</v>
+        <v>0.9963753506644903</v>
       </c>
       <c r="Y140">
         <v>0.9952961802482605</v>
@@ -13354,7 +13354,7 @@
         <v>182.2500582624662</v>
       </c>
       <c r="E141">
-        <v>184.88</v>
+        <v>184.91</v>
       </c>
       <c r="F141">
         <v>163.9</v>
@@ -13363,16 +13363,16 @@
         <v>347164.85315625</v>
       </c>
       <c r="H141">
-        <v>312562.29999999993</v>
+        <v>316625.7599999987</v>
       </c>
       <c r="I141">
-        <v>283899.319999999</v>
+        <v>282233.33999999973</v>
       </c>
       <c r="J141">
-        <v>-0.18223484486137428</v>
+        <v>-0.18703366013559639</v>
       </c>
       <c r="K141">
-        <v>-0.09967182115833706</v>
+        <v>-0.08796712247396321</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>0.9981385171413422</v>
       </c>
       <c r="X141">
-        <v>0.9981138822424412</v>
+        <v>0.9981138620061547</v>
       </c>
       <c r="Y141">
         <v>0.9968446493148804</v>
@@ -13458,16 +13458,16 @@
         <v>266747.127828125</v>
       </c>
       <c r="H142">
-        <v>238788.8099999997</v>
+        <v>238746.86000000016</v>
       </c>
       <c r="I142">
-        <v>238206.6699999995</v>
+        <v>238359.60000000015</v>
       </c>
       <c r="J142">
-        <v>-0.10699443349401386</v>
+        <v>-0.10642111897983023</v>
       </c>
       <c r="K142">
-        <v>-0.1048120669780553</v>
+        <v>-0.10496933202657188</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>260.2555420115263</v>
       </c>
       <c r="E143">
-        <v>264.93</v>
+        <v>264.89</v>
       </c>
       <c r="F143">
         <v>260.26</v>
@@ -13538,16 +13538,16 @@
         <v>563315.7418125</v>
       </c>
       <c r="H143">
-        <v>455595.5499999991</v>
+        <v>456403.4299999994</v>
       </c>
       <c r="I143">
-        <v>450369.3199999993</v>
+        <v>450292.62</v>
       </c>
       <c r="J143">
-        <v>-0.20050286798144373</v>
+        <v>-0.20063902607948042</v>
       </c>
       <c r="K143">
-        <v>-0.19122524690310477</v>
+        <v>-0.18979109560919472</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>0.9996044635772705</v>
       </c>
       <c r="X143">
-        <v>0.9996037575511051</v>
+        <v>0.9996037820810063</v>
       </c>
       <c r="Y143">
         <v>0.9994428753852844</v>
@@ -13624,7 +13624,7 @@
         <v>253.61051516371649</v>
       </c>
       <c r="E144">
-        <v>256.54</v>
+        <v>256.55</v>
       </c>
       <c r="F144">
         <v>253.61</v>
@@ -13633,16 +13633,16 @@
         <v>523254.5668046875</v>
       </c>
       <c r="H144">
-        <v>434887.4800000018</v>
+        <v>434278.69000000233</v>
       </c>
       <c r="I144">
-        <v>437349.7499999997</v>
+        <v>434795.069999998</v>
       </c>
       <c r="J144">
-        <v>-0.16417404119236867</v>
+        <v>-0.1690563301623477</v>
       </c>
       <c r="K144">
-        <v>-0.16887972396363246</v>
+        <v>-0.1700431920700211</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>0.9998345375061035</v>
       </c>
       <c r="X144">
-        <v>0.9998347675485403</v>
+        <v>0.9998347954041495</v>
       </c>
       <c r="Y144">
         <v>0.9996781349182129</v>
@@ -13719,7 +13719,7 @@
         <v>231.3998515584731</v>
       </c>
       <c r="E145">
-        <v>233.86</v>
+        <v>233.95</v>
       </c>
       <c r="F145">
         <v>231.4</v>
@@ -13728,16 +13728,16 @@
         <v>472797.409234375</v>
       </c>
       <c r="H145">
-        <v>398682.77999999974</v>
+        <v>398225.2600000014</v>
       </c>
       <c r="I145">
-        <v>400080.2299999992</v>
+        <v>399804.5899999996</v>
       </c>
       <c r="J145">
-        <v>-0.15380198328948208</v>
+        <v>-0.15438498140794887</v>
       </c>
       <c r="K145">
-        <v>-0.15675768899493941</v>
+        <v>-0.15772537619258972</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>0.9994998872280121</v>
       </c>
       <c r="X145">
-        <v>0.9995031003818506</v>
+        <v>0.9995030185404734</v>
       </c>
       <c r="Y145">
         <v>0.9992192983627319</v>
@@ -13814,7 +13814,7 @@
         <v>257.7667583610704</v>
       </c>
       <c r="E146">
-        <v>260.7</v>
+        <v>260.84</v>
       </c>
       <c r="F146">
         <v>257.77</v>
@@ -13823,16 +13823,16 @@
         <v>512843.652609375</v>
       </c>
       <c r="H146">
-        <v>438767.9599999993</v>
+        <v>438217.5799999993</v>
       </c>
       <c r="I146">
-        <v>442906.8200000014</v>
+        <v>442009.96000000095</v>
       </c>
       <c r="J146">
-        <v>-0.1363706701906739</v>
+        <v>-0.13811946828037858</v>
       </c>
       <c r="K146">
-        <v>-0.144441083032762</v>
+        <v>-0.14551427560753533</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>0.9968112707138062</v>
       </c>
       <c r="X146">
-        <v>0.9968155891559053</v>
+        <v>0.9968157246346775</v>
       </c>
       <c r="Y146">
         <v>0.9939314126968384</v>
@@ -13909,7 +13909,7 @@
         <v>241.60142415078306</v>
       </c>
       <c r="E147">
-        <v>244.51</v>
+        <v>244.47</v>
       </c>
       <c r="F147">
         <v>241.6</v>
@@ -13918,16 +13918,16 @@
         <v>525579.8390625</v>
       </c>
       <c r="H147">
-        <v>403574.4300000003</v>
+        <v>401771.24999999924</v>
       </c>
       <c r="I147">
-        <v>402090.1799999993</v>
+        <v>400355.49999999785</v>
       </c>
       <c r="J147">
-        <v>-0.23495889660222644</v>
+        <v>-0.2382594037204136</v>
       </c>
       <c r="K147">
-        <v>-0.23213487275335026</v>
+        <v>-0.2355657121158674</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>0.9985548853874207</v>
       </c>
       <c r="X147">
-        <v>0.9985614676881536</v>
+        <v>0.998561398461701</v>
       </c>
       <c r="Y147">
         <v>0.997363269329071</v>
@@ -14004,7 +14004,7 @@
         <v>258.1596771816526</v>
       </c>
       <c r="E148">
-        <v>264.51</v>
+        <v>264.47</v>
       </c>
       <c r="F148">
         <v>258.16</v>
@@ -14013,16 +14013,16 @@
         <v>546920.7775625</v>
       </c>
       <c r="H148">
-        <v>441581.96000000084</v>
+        <v>442098.61000000127</v>
       </c>
       <c r="I148">
-        <v>440905.1100000001</v>
+        <v>440937.0300000006</v>
       </c>
       <c r="J148">
-        <v>-0.19384099473234004</v>
+        <v>-0.193782631617772</v>
       </c>
       <c r="K148">
-        <v>-0.19260342975443356</v>
+        <v>-0.19165877740038875</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>0.9938002824783325</v>
       </c>
       <c r="X148">
-        <v>0.9938200412489485</v>
+        <v>0.9938183086927713</v>
       </c>
       <c r="Y148">
         <v>0.9893860816955566</v>
@@ -14099,7 +14099,7 @@
         <v>235.85415400334225</v>
       </c>
       <c r="E149">
-        <v>235.91</v>
+        <v>235.92</v>
       </c>
       <c r="F149">
         <v>235.85</v>
@@ -14108,16 +14108,16 @@
         <v>476830.56139843754</v>
       </c>
       <c r="H149">
-        <v>400160.7999999997</v>
+        <v>399247.6799999991</v>
       </c>
       <c r="I149">
-        <v>403443.0499999996</v>
+        <v>401905.8999999998</v>
       </c>
       <c r="J149">
-        <v>-0.15390689552953313</v>
+        <v>-0.1571305773243654</v>
       </c>
       <c r="K149">
-        <v>-0.1607903679109463</v>
+        <v>-0.16270534583795374</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>0.9324042995770773</v>
       </c>
       <c r="X149">
-        <v>0.9081188898760931</v>
+        <v>0.9081160103357161</v>
       </c>
       <c r="Y149">
         <v>0.8353248834609985</v>
@@ -14194,7 +14194,7 @@
         <v>245.01354357281775</v>
       </c>
       <c r="E150">
-        <v>247.32</v>
+        <v>247.29</v>
       </c>
       <c r="F150">
         <v>245.01</v>
@@ -14203,16 +14203,16 @@
         <v>497980.33900000004</v>
       </c>
       <c r="H150">
-        <v>417291.38999999914</v>
+        <v>417814.1299999998</v>
       </c>
       <c r="I150">
-        <v>421583.06999999983</v>
+        <v>421154.77999999904</v>
       </c>
       <c r="J150">
-        <v>-0.15341422746410918</v>
+        <v>-0.15427428149929628</v>
       </c>
       <c r="K150">
-        <v>-0.16203239903413313</v>
+        <v>-0.1609826788764049</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>0.9988549947738647</v>
       </c>
       <c r="X150">
-        <v>0.9988572328620222</v>
+        <v>0.9988570000890512</v>
       </c>
       <c r="Y150">
         <v>0.9977966547012329</v>
@@ -14289,7 +14289,7 @@
         <v>145.95781184339836</v>
       </c>
       <c r="E151">
-        <v>147.99</v>
+        <v>147.91</v>
       </c>
       <c r="F151">
         <v>145.96</v>
@@ -14298,16 +14298,16 @@
         <v>284257.5098125</v>
       </c>
       <c r="H151">
-        <v>254178.1699999999</v>
+        <v>253790.5099999996</v>
       </c>
       <c r="I151">
-        <v>252562.56000000078</v>
+        <v>252340.89999999927</v>
       </c>
       <c r="J151">
-        <v>-0.11150083539888042</v>
+        <v>-0.1122806213054963</v>
       </c>
       <c r="K151">
-        <v>-0.10581722126652278</v>
+        <v>-0.10718098470853704</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>0.9997608065605164</v>
       </c>
       <c r="X151">
-        <v>0.9997610207289575</v>
+        <v>0.9997610150389189</v>
       </c>
       <c r="Y151">
         <v>0.9997268319129944</v>
@@ -14384,7 +14384,7 @@
         <v>155.0237211642884</v>
       </c>
       <c r="E152">
-        <v>157.88</v>
+        <v>157.76</v>
       </c>
       <c r="F152">
         <v>155.02</v>
@@ -14393,16 +14393,16 @@
         <v>305686.298265625</v>
       </c>
       <c r="H152">
-        <v>268738.0599999995</v>
+        <v>268623.59999999986</v>
       </c>
       <c r="I152">
-        <v>267924.8799999999</v>
+        <v>267867.45999999944</v>
       </c>
       <c r="J152">
-        <v>-0.12352996676616655</v>
+        <v>-0.1237178063923658</v>
       </c>
       <c r="K152">
-        <v>-0.120869788653463</v>
+        <v>-0.12124422480139971</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>0.9992047846317291</v>
       </c>
       <c r="X152">
-        <v>0.9992047855836977</v>
+        <v>0.9992047530342302</v>
       </c>
       <c r="Y152">
         <v>0.9987229704856873</v>
@@ -14479,7 +14479,7 @@
         <v>140.4958613046705</v>
       </c>
       <c r="E153">
-        <v>142.27</v>
+        <v>142.3</v>
       </c>
       <c r="F153">
         <v>140.5</v>
@@ -14488,16 +14488,16 @@
         <v>267973.521046875</v>
       </c>
       <c r="H153">
-        <v>245691.38000000053</v>
+        <v>245520.55000000008</v>
       </c>
       <c r="I153">
-        <v>243157.2699999988</v>
+        <v>243484.85999999967</v>
       </c>
       <c r="J153">
-        <v>-0.0926071014402025</v>
+        <v>-0.09138462991122047</v>
       </c>
       <c r="K153">
-        <v>-0.08315053278333712</v>
+        <v>-0.08378802114163865</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>0.9999502301216125</v>
       </c>
       <c r="X153">
-        <v>0.9999502304671578</v>
+        <v>0.9999502304692308</v>
       </c>
       <c r="Y153">
         <v>0.9999499320983887</v>
@@ -14574,7 +14574,7 @@
         <v>149.5704646425458</v>
       </c>
       <c r="E154">
-        <v>153.34</v>
+        <v>153.43</v>
       </c>
       <c r="F154">
         <v>149.57</v>
@@ -14583,16 +14583,16 @@
         <v>281720.35059375</v>
       </c>
       <c r="H154">
-        <v>260674.2500000001</v>
+        <v>259746.18999999974</v>
       </c>
       <c r="I154">
-        <v>258972.27000000008</v>
+        <v>257451.46000000017</v>
       </c>
       <c r="J154">
-        <v>-0.08074702642463134</v>
+        <v>-0.0861453229864334</v>
       </c>
       <c r="K154">
-        <v>-0.07470564533017743</v>
+        <v>-0.0779999050385882</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>0.9990952908992767</v>
       </c>
       <c r="X154">
-        <v>0.9990961748535924</v>
+        <v>0.9990960945220295</v>
       </c>
       <c r="Y154">
         <v>0.9986298084259033</v>
@@ -14669,7 +14669,7 @@
         <v>168.26990672539043</v>
       </c>
       <c r="E155">
-        <v>170.38</v>
+        <v>170.33</v>
       </c>
       <c r="F155">
         <v>168.27</v>
@@ -14678,16 +14678,16 @@
         <v>381723.2231875</v>
       </c>
       <c r="H155">
-        <v>291951.46999999863</v>
+        <v>292550.9600000003</v>
       </c>
       <c r="I155">
-        <v>290178.1899999998</v>
+        <v>289867.32999999984</v>
       </c>
       <c r="J155">
-        <v>-0.2398204448319191</v>
+        <v>-0.24063480450698477</v>
       </c>
       <c r="K155">
-        <v>-0.2351749847386311</v>
+        <v>-0.23360450130040653</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>0.9966036379337311</v>
       </c>
       <c r="X155">
-        <v>0.9966074588258224</v>
+        <v>0.9966074847833247</v>
       </c>
       <c r="Y155">
         <v>0.9952699542045593</v>
@@ -14764,7 +14764,7 @@
         <v>168.17110196732688</v>
       </c>
       <c r="E156">
-        <v>168.82</v>
+        <v>168.73</v>
       </c>
       <c r="F156">
         <v>168.17</v>
@@ -14773,16 +14773,16 @@
         <v>381905.5825625</v>
       </c>
       <c r="H156">
-        <v>290562.829999999</v>
+        <v>290541.340000001</v>
       </c>
       <c r="I156">
-        <v>290444.5499999998</v>
+        <v>289398.75</v>
       </c>
       <c r="J156">
-        <v>-0.23948597962045326</v>
+        <v>-0.24222435278845655</v>
       </c>
       <c r="K156">
-        <v>-0.23917626956278515</v>
+        <v>-0.239232540015429</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>0.9990716278553009</v>
       </c>
       <c r="X156">
-        <v>0.999071525559167</v>
+        <v>0.9990715233073184</v>
       </c>
       <c r="Y156">
         <v>0.9990266561508179</v>
@@ -14859,7 +14859,7 @@
         <v>171.08450891748635</v>
       </c>
       <c r="E157">
-        <v>172.9</v>
+        <v>172.94</v>
       </c>
       <c r="F157">
         <v>171.57</v>
@@ -14868,16 +14868,16 @@
         <v>382365.685</v>
       </c>
       <c r="H157">
-        <v>296731.31999999896</v>
+        <v>295564.38000000047</v>
       </c>
       <c r="I157">
-        <v>296290.1199999992</v>
+        <v>292574.28000000096</v>
       </c>
       <c r="J157">
-        <v>-0.22511320543840335</v>
+        <v>-0.23483123230579397</v>
       </c>
       <c r="K157">
-        <v>-0.2239593362045578</v>
+        <v>-0.22701123140796364</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>0.9909116625785828</v>
       </c>
       <c r="X157">
-        <v>0.9909476073661188</v>
+        <v>0.9909473754657326</v>
       </c>
       <c r="Y157">
         <v>0.9856249690055847</v>
@@ -14954,7 +14954,7 @@
         <v>144.32549262094253</v>
       </c>
       <c r="E158">
-        <v>146.71</v>
+        <v>146.7</v>
       </c>
       <c r="F158">
         <v>144.31</v>
@@ -14963,16 +14963,16 @@
         <v>292072.828578125</v>
       </c>
       <c r="H158">
-        <v>249324.5000000007</v>
+        <v>248853.73000000019</v>
       </c>
       <c r="I158">
-        <v>248726.48999999987</v>
+        <v>249197.88000000015</v>
       </c>
       <c r="J158">
-        <v>-0.1484093497815071</v>
+        <v>-0.14679540300564606</v>
       </c>
       <c r="K158">
-        <v>-0.14636188099465666</v>
+        <v>-0.14797370501229065</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>0.9931510090827942</v>
       </c>
       <c r="X158">
-        <v>0.9931580479032972</v>
+        <v>0.9931562097692986</v>
       </c>
       <c r="Y158">
         <v>0.988837480545044</v>
@@ -15049,7 +15049,7 @@
         <v>175.91130337677518</v>
       </c>
       <c r="E159">
-        <v>176.91</v>
+        <v>177.05</v>
       </c>
       <c r="F159">
         <v>175.91</v>
@@ -15058,16 +15058,16 @@
         <v>418586.63215625</v>
       </c>
       <c r="H159">
-        <v>305108.91000000003</v>
+        <v>304617.2199999998</v>
       </c>
       <c r="I159">
-        <v>304249.4000000001</v>
+        <v>302725.609999999</v>
       </c>
       <c r="J159">
-        <v>-0.2731507013668084</v>
+        <v>-0.2767910230659311</v>
       </c>
       <c r="K159">
-        <v>-0.2710973390901098</v>
+        <v>-0.2722719824308859</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>0.9990014433860779</v>
       </c>
       <c r="X159">
-        <v>0.9990011240459323</v>
+        <v>0.9990011223721634</v>
       </c>
       <c r="Y159">
         <v>0.9989663362503052</v>
@@ -15144,7 +15144,7 @@
         <v>176.92465514787213</v>
       </c>
       <c r="E160">
-        <v>178.34</v>
+        <v>178.33</v>
       </c>
       <c r="F160">
         <v>176.92</v>
@@ -15153,16 +15153,16 @@
         <v>391010.18684375</v>
       </c>
       <c r="H160">
-        <v>307873.5600000004</v>
+        <v>307459.1999999988</v>
       </c>
       <c r="I160">
-        <v>313898.24000000005</v>
+        <v>301006.9700000002</v>
       </c>
       <c r="J160">
-        <v>-0.19721211732666277</v>
+        <v>-0.2301812583714491</v>
       </c>
       <c r="K160">
-        <v>-0.212620104644413</v>
+        <v>-0.21367982128081664</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>0.9835693538188934</v>
       </c>
       <c r="X160">
-        <v>0.9835735655565582</v>
+        <v>0.9835570895523541</v>
       </c>
       <c r="Y160">
         <v>0.9693467020988464</v>
@@ -15239,7 +15239,7 @@
         <v>174.74373677595116</v>
       </c>
       <c r="E161">
-        <v>176.63</v>
+        <v>176.54</v>
       </c>
       <c r="F161">
         <v>174.59</v>
@@ -15248,16 +15248,16 @@
         <v>357237.259546875</v>
       </c>
       <c r="H161">
-        <v>304824.7799999997</v>
+        <v>303316.42999999993</v>
       </c>
       <c r="I161">
-        <v>301642.8700000003</v>
+        <v>301650.05000000127</v>
       </c>
       <c r="J161">
-        <v>-0.15562315537128316</v>
+        <v>-0.15560305668390073</v>
       </c>
       <c r="K161">
-        <v>-0.1467161617277999</v>
+        <v>-0.15093842567057272</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>0.9924811720848083</v>
       </c>
       <c r="X161">
-        <v>0.9924849116721597</v>
+        <v>0.9924864406591836</v>
       </c>
       <c r="Y161">
         <v>0.9868263006210327</v>
@@ -15334,7 +15334,7 @@
         <v>144.10569131965207</v>
       </c>
       <c r="E162">
-        <v>144.86</v>
+        <v>144.94</v>
       </c>
       <c r="F162">
         <v>144.11</v>
@@ -15343,16 +15343,16 @@
         <v>325187.18306250003</v>
       </c>
       <c r="H162">
-        <v>249071.4900000003</v>
+        <v>249544.79000000036</v>
       </c>
       <c r="I162">
-        <v>249301.61000000022</v>
+        <v>249321.8700000003</v>
       </c>
       <c r="J162">
-        <v>-0.23335966795442495</v>
+        <v>-0.23329736537592458</v>
       </c>
       <c r="K162">
-        <v>-0.23406732192108107</v>
+        <v>-0.23261185250330554</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>0.9930827617645264</v>
       </c>
       <c r="X162">
-        <v>0.9930666772816588</v>
+        <v>0.9930735504237387</v>
       </c>
       <c r="Y162">
         <v>0.9872758984565735</v>
@@ -15429,7 +15429,7 @@
         <v>178.17608781563666</v>
       </c>
       <c r="E163">
-        <v>178.92</v>
+        <v>178.85</v>
       </c>
       <c r="F163">
         <v>178.18</v>
@@ -15438,16 +15438,16 @@
         <v>396067.8980625</v>
       </c>
       <c r="H163">
-        <v>309218.61999999936</v>
+        <v>308633.2699999994</v>
       </c>
       <c r="I163">
-        <v>308473.6400000001</v>
+        <v>308165.5500000011</v>
       </c>
       <c r="J163">
-        <v>-0.22115970138200255</v>
+        <v>-0.22193757305881884</v>
       </c>
       <c r="K163">
-        <v>-0.21927876126127172</v>
+        <v>-0.2207566644260155</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>0.9964579939842224</v>
       </c>
       <c r="X163">
-        <v>0.9964580777084108</v>
+        <v>0.9964576340410278</v>
       </c>
       <c r="Y163">
         <v>0.995564341545105</v>
@@ -15524,7 +15524,7 @@
         <v>173.87833387032805</v>
       </c>
       <c r="E164">
-        <v>174.72</v>
+        <v>174.65</v>
       </c>
       <c r="F164">
         <v>173.88</v>
@@ -15533,16 +15533,16 @@
         <v>390472.19337500003</v>
       </c>
       <c r="H164">
-        <v>301777.4599999994</v>
+        <v>301869.9600000007</v>
       </c>
       <c r="I164">
-        <v>300916.9400000008</v>
+        <v>302189.95999999996</v>
       </c>
       <c r="J164">
-        <v>-0.22935116736723046</v>
+        <v>-0.22609096082346625</v>
       </c>
       <c r="K164">
-        <v>-0.22714737407644384</v>
+        <v>-0.22691048140759124</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>0.9969789981842041</v>
       </c>
       <c r="X164">
-        <v>0.9969668895666628</v>
+        <v>0.9969667633005841</v>
       </c>
       <c r="Y164">
         <v>0.9959560036659241</v>
@@ -15619,7 +15619,7 @@
         <v>181.6096663803425</v>
       </c>
       <c r="E165">
-        <v>182.8</v>
+        <v>181.83</v>
       </c>
       <c r="F165">
         <v>178.42</v>
@@ -15628,16 +15628,16 @@
         <v>397127.274921875</v>
       </c>
       <c r="H165">
-        <v>315561.0600000009</v>
+        <v>314411.0199999991</v>
       </c>
       <c r="I165">
-        <v>299533.3599999998</v>
+        <v>311015.5800000001</v>
       </c>
       <c r="J165">
-        <v>-0.2457497157330087</v>
+        <v>-0.21683651655206826</v>
       </c>
       <c r="K165">
-        <v>-0.20539061422542734</v>
+        <v>-0.20828651202098442</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>0.9964845478534698</v>
       </c>
       <c r="X165">
-        <v>0.9964671802201583</v>
+        <v>0.9964625275199721</v>
       </c>
       <c r="Y165">
         <v>0.9956718683242798</v>
@@ -15714,7 +15714,7 @@
         <v>165.9439743132166</v>
       </c>
       <c r="E166">
-        <v>167.81</v>
+        <v>167.65</v>
       </c>
       <c r="F166">
         <v>160.07</v>
@@ -15723,16 +15723,16 @@
         <v>332740.90965625003</v>
       </c>
       <c r="H166">
-        <v>288799.20999999926</v>
+        <v>286832.6699999999</v>
       </c>
       <c r="I166">
-        <v>277210.9500000009</v>
+        <v>277301.84000000096</v>
       </c>
       <c r="J166">
-        <v>-0.16688648147778515</v>
+        <v>-0.16661332600647874</v>
       </c>
       <c r="K166">
-        <v>-0.13205980503463288</v>
+        <v>-0.13796992892661522</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>0.9847228825092316</v>
       </c>
       <c r="X166">
-        <v>0.9847950173114982</v>
+        <v>0.9847982163079286</v>
       </c>
       <c r="Y166">
         <v>0.9790119528770447</v>
@@ -15809,7 +15809,7 @@
         <v>177.5257085635874</v>
       </c>
       <c r="E167">
-        <v>178.63</v>
+        <v>178.7</v>
       </c>
       <c r="F167">
         <v>177.53</v>
@@ -15818,16 +15818,16 @@
         <v>391442.1318125</v>
       </c>
       <c r="H167">
-        <v>308241.8700000002</v>
+        <v>307754.5100000005</v>
       </c>
       <c r="I167">
-        <v>306553.8000000003</v>
+        <v>304969.66999999975</v>
       </c>
       <c r="J167">
-        <v>-0.21686048821428622</v>
+        <v>-0.220907395461254</v>
       </c>
       <c r="K167">
-        <v>-0.21254805002020719</v>
+        <v>-0.21379308717996084</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>0.9958295524120331</v>
       </c>
       <c r="X167">
-        <v>0.9958428512707169</v>
+        <v>0.9958443858003891</v>
       </c>
       <c r="Y167">
         <v>0.9929322004318237</v>
@@ -15904,7 +15904,7 @@
         <v>182.2451198719885</v>
       </c>
       <c r="E168">
-        <v>183.6</v>
+        <v>183.57</v>
       </c>
       <c r="F168">
         <v>181.15</v>
@@ -15913,16 +15913,16 @@
         <v>388661.693125</v>
       </c>
       <c r="H168">
-        <v>317511.0200000006</v>
+        <v>316169.9600000003</v>
       </c>
       <c r="I168">
-        <v>313303.5200000002</v>
+        <v>306860.11999999994</v>
       </c>
       <c r="J168">
-        <v>-0.19389143426790809</v>
+        <v>-0.2104698625359287</v>
       </c>
       <c r="K168">
-        <v>-0.18306582404074528</v>
+        <v>-0.18651627985803362</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>0.9703018367290497</v>
       </c>
       <c r="X168">
-        <v>0.9703056267481566</v>
+        <v>0.9703033310050496</v>
       </c>
       <c r="Y168">
         <v>0.9594538807868958</v>
@@ -15999,7 +15999,7 @@
         <v>183.0021981856258</v>
       </c>
       <c r="E169">
-        <v>184.92</v>
+        <v>184.76</v>
       </c>
       <c r="F169">
         <v>183.02</v>
@@ -16008,16 +16008,16 @@
         <v>382211.53356250003</v>
       </c>
       <c r="H169">
-        <v>319528.4299999988</v>
+        <v>317454.92000000057</v>
       </c>
       <c r="I169">
-        <v>316472.6199999997</v>
+        <v>313300.1199999991</v>
       </c>
       <c r="J169">
-        <v>-0.17199615341212762</v>
+        <v>-0.18029653087701072</v>
       </c>
       <c r="K169">
-        <v>-0.16400107808952638</v>
+        <v>-0.16942611061188798</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>0.9958722591400146</v>
       </c>
       <c r="X169">
-        <v>0.9958875829827162</v>
+        <v>0.9958866607807569</v>
       </c>
       <c r="Y169">
         <v>0.9926741719245911</v>
@@ -16094,7 +16094,7 @@
         <v>146.18670826648344</v>
       </c>
       <c r="E170">
-        <v>150.97</v>
+        <v>151.02</v>
       </c>
       <c r="F170">
         <v>146.25</v>
@@ -16103,16 +16103,16 @@
         <v>316954.26871875</v>
       </c>
       <c r="H170">
-        <v>254844.28000000023</v>
+        <v>255025.84999999954</v>
       </c>
       <c r="I170">
-        <v>245893.3800000004</v>
+        <v>253615.05000000005</v>
       </c>
       <c r="J170">
-        <v>-0.2241991849676131</v>
+        <v>-0.1998370899839627</v>
       </c>
       <c r="K170">
-        <v>-0.19595883333523795</v>
+        <v>-0.1953859746678558</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>0.9813437461853027</v>
       </c>
       <c r="X170">
-        <v>0.9813388368210512</v>
+        <v>0.9813196332100368</v>
       </c>
       <c r="Y170">
         <v>0.9642569422721863</v>
@@ -16189,7 +16189,7 @@
         <v>177.7261031522626</v>
       </c>
       <c r="E171">
-        <v>179.75</v>
+        <v>179.8</v>
       </c>
       <c r="F171">
         <v>177.73</v>
@@ -16198,16 +16198,16 @@
         <v>401683.9165</v>
       </c>
       <c r="H171">
-        <v>309219.29999999877</v>
+        <v>307787.95999999985</v>
       </c>
       <c r="I171">
-        <v>307094.51999999967</v>
+        <v>305953.1300000001</v>
       </c>
       <c r="J171">
-        <v>-0.23548216051114987</v>
+        <v>-0.23832367333532478</v>
       </c>
       <c r="K171">
-        <v>-0.2301924789662352</v>
+        <v>-0.23375582801060482</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>0.9966762661933899</v>
       </c>
       <c r="X171">
-        <v>0.9966743026958563</v>
+        <v>0.9966740059738575</v>
       </c>
       <c r="Y171">
         <v>0.9959028363227844</v>
@@ -16284,7 +16284,7 @@
         <v>180.01351654135811</v>
       </c>
       <c r="E172">
-        <v>181.23</v>
+        <v>181.2</v>
       </c>
       <c r="F172">
         <v>180.01</v>
@@ -16293,16 +16293,16 @@
         <v>394628.5514375</v>
       </c>
       <c r="H172">
-        <v>314208.0000000008</v>
+        <v>312860.9500000001</v>
       </c>
       <c r="I172">
-        <v>319679.12999999966</v>
+        <v>307779.6900000007</v>
       </c>
       <c r="J172">
-        <v>-0.18992397069214742</v>
+        <v>-0.22007749089906925</v>
       </c>
       <c r="K172">
-        <v>-0.20378797009125155</v>
+        <v>-0.20720143319495715</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>0.9998389184474945</v>
       </c>
       <c r="X172">
-        <v>0.9998387788766706</v>
+        <v>0.999838779685007</v>
       </c>
       <c r="Y172">
         <v>0.9998196959495544</v>
@@ -16379,7 +16379,7 @@
         <v>167.1863812934429</v>
       </c>
       <c r="E173">
-        <v>167.8</v>
+        <v>167.71</v>
       </c>
       <c r="F173">
         <v>167.21</v>
@@ -16388,16 +16388,16 @@
         <v>373495.5214375</v>
       </c>
       <c r="H173">
-        <v>290168.08000000025</v>
+        <v>290044.55000000034</v>
       </c>
       <c r="I173">
-        <v>275906.0199999995</v>
+        <v>290152.88999999926</v>
       </c>
       <c r="J173">
-        <v>-0.26128693876140885</v>
+        <v>-0.22314225112187094</v>
       </c>
       <c r="K173">
-        <v>-0.22310158129016178</v>
+        <v>-0.22343232153444764</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>0.9985249936580658</v>
       </c>
       <c r="X173">
-        <v>0.998524778208202</v>
+        <v>0.9985249113592519</v>
       </c>
       <c r="Y173">
         <v>0.997835099697113</v>
@@ -16474,7 +16474,7 @@
         <v>144.30366715892978</v>
       </c>
       <c r="E174">
-        <v>145.68</v>
+        <v>145.62</v>
       </c>
       <c r="F174">
         <v>144.27</v>
@@ -16483,16 +16483,16 @@
         <v>270925.593546875</v>
       </c>
       <c r="H174">
-        <v>250831.43999999977</v>
+        <v>252034.26000000015</v>
       </c>
       <c r="I174">
-        <v>249855.9300000001</v>
+        <v>250039.27000000046</v>
       </c>
       <c r="J174">
-        <v>-0.07776918847362221</v>
+        <v>-0.07709247130711123</v>
       </c>
       <c r="K174">
-        <v>-0.07416853197148603</v>
+        <v>-0.0697288628200654</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>0.9920758903026581</v>
       </c>
       <c r="X174">
-        <v>0.9920796337866538</v>
+        <v>0.9920809724182068</v>
       </c>
       <c r="Y174">
         <v>0.9890363812446594</v>
@@ -16569,7 +16569,7 @@
         <v>175.93186067812684</v>
       </c>
       <c r="E175">
-        <v>177.97</v>
+        <v>178.0</v>
       </c>
       <c r="F175">
         <v>175.93</v>
@@ -16578,16 +16578,16 @@
         <v>387557.4593125</v>
       </c>
       <c r="H175">
-        <v>303470.99000000104</v>
+        <v>303429.3799999996</v>
       </c>
       <c r="I175">
-        <v>302738.5400000003</v>
+        <v>301481.0799999995</v>
       </c>
       <c r="J175">
-        <v>-0.2188550814193141</v>
+        <v>-0.2220996583711588</v>
       </c>
       <c r="K175">
-        <v>-0.2169651681112332</v>
+        <v>-0.21707253283613168</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>0.9961031973361969</v>
       </c>
       <c r="X175">
-        <v>0.9960758324731068</v>
+        <v>0.9960760451174365</v>
       </c>
       <c r="Y175">
         <v>0.9945025444030762</v>
@@ -16664,7 +16664,7 @@
         <v>184.8359152582617</v>
       </c>
       <c r="E176">
-        <v>188.08</v>
+        <v>186.33</v>
       </c>
       <c r="F176">
         <v>187.35</v>
@@ -16673,16 +16673,16 @@
         <v>403500.8696875</v>
       </c>
       <c r="H176">
-        <v>324956.82000000024</v>
+        <v>321701.4600000003</v>
       </c>
       <c r="I176">
-        <v>324315.7499999985</v>
+        <v>323982.08000000013</v>
       </c>
       <c r="J176">
-        <v>-0.19624522680416562</v>
+        <v>-0.1970721643031028</v>
       </c>
       <c r="K176">
-        <v>-0.1946564569943304</v>
+        <v>-0.2027242462967949</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>0.9995307326316833</v>
       </c>
       <c r="X176">
-        <v>0.9995309605807196</v>
+        <v>0.9995310486005828</v>
       </c>
       <c r="Y176">
         <v>0.9995212554931641</v>
@@ -16759,7 +16759,7 @@
         <v>143.1194388419227</v>
       </c>
       <c r="E177">
-        <v>147.42</v>
+        <v>147.52</v>
       </c>
       <c r="F177">
         <v>137.51</v>
@@ -16768,16 +16768,16 @@
         <v>288564.645359375</v>
       </c>
       <c r="H177">
-        <v>249462.3200000013</v>
+        <v>249127.26000000024</v>
       </c>
       <c r="I177">
-        <v>238008.40999999954</v>
+        <v>237634.9100000003</v>
       </c>
       <c r="J177">
-        <v>-0.1751989932668755</v>
+        <v>-0.17649333062249328</v>
       </c>
       <c r="K177">
-        <v>-0.1355062929163624</v>
+        <v>-0.13666741921991135</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>0.9980078041553497</v>
       </c>
       <c r="X177">
-        <v>0.9980090694803295</v>
+        <v>0.9980082435780824</v>
       </c>
       <c r="Y177">
         <v>0.9960752129554749</v>
@@ -16854,7 +16854,7 @@
         <v>176.161158604652</v>
       </c>
       <c r="E178">
-        <v>177.28</v>
+        <v>177.39</v>
       </c>
       <c r="F178">
         <v>176.16</v>
@@ -16863,16 +16863,16 @@
         <v>391723.7508125</v>
       </c>
       <c r="H178">
-        <v>300689.82000000076</v>
+        <v>299969.5800000005</v>
       </c>
       <c r="I178">
-        <v>297614.87000000017</v>
+        <v>295965.75999999885</v>
       </c>
       <c r="J178">
-        <v>-0.24024297892916224</v>
+        <v>-0.2444528589698307</v>
       </c>
       <c r="K178">
-        <v>-0.2323931868406748</v>
+        <v>-0.2342318295027712</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>0.9985491633415222</v>
       </c>
       <c r="X178">
-        <v>0.9985490405471604</v>
+        <v>0.9985490547526957</v>
       </c>
       <c r="Y178">
         <v>0.9980341792106628</v>
@@ -16949,7 +16949,7 @@
         <v>177.55295425343468</v>
       </c>
       <c r="E179">
-        <v>178.84</v>
+        <v>178.81</v>
       </c>
       <c r="F179">
         <v>177.55</v>
@@ -16958,16 +16958,16 @@
         <v>412931.2</v>
       </c>
       <c r="H179">
-        <v>302470.55</v>
+        <v>302644.8399999996</v>
       </c>
       <c r="I179">
-        <v>301327.130000001</v>
+        <v>296763.4800000008</v>
       </c>
       <c r="J179">
-        <v>-0.27027279604931526</v>
+        <v>-0.2813246371308325</v>
       </c>
       <c r="K179">
-        <v>-0.26750376333878384</v>
+        <v>-0.2670816833409546</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>0.99736288189888</v>
       </c>
       <c r="X179">
-        <v>0.9973594166860766</v>
+        <v>0.997358580468467</v>
       </c>
       <c r="Y179">
         <v>0.9957711100578308</v>
@@ -17044,7 +17044,7 @@
         <v>168.40255887046447</v>
       </c>
       <c r="E180">
-        <v>171.57</v>
+        <v>169.25</v>
       </c>
       <c r="F180">
         <v>167.03</v>
@@ -17053,16 +17053,16 @@
         <v>368643.902671875</v>
       </c>
       <c r="H180">
-        <v>292905.53000000055</v>
+        <v>283288.60999999876</v>
       </c>
       <c r="I180">
-        <v>283888.42000000033</v>
+        <v>280520.5799999998</v>
       </c>
       <c r="J180">
-        <v>-0.22991152724235997</v>
+        <v>-0.2390472812195476</v>
       </c>
       <c r="K180">
-        <v>-0.20545130984924542</v>
+        <v>-0.23153859877576724</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>0.9786699712276459</v>
       </c>
       <c r="X180">
-        <v>0.979031492147254</v>
+        <v>0.9792962282634099</v>
       </c>
       <c r="Y180">
         <v>0.9598573446273804</v>
@@ -17139,7 +17139,7 @@
         <v>153.9299155486634</v>
       </c>
       <c r="E181">
-        <v>155.33</v>
+        <v>155.43</v>
       </c>
       <c r="F181">
         <v>153.91</v>
@@ -17148,16 +17148,16 @@
         <v>297425.09359375003</v>
       </c>
       <c r="H181">
-        <v>266486.3200000006</v>
+        <v>263575.3800000006</v>
       </c>
       <c r="I181">
-        <v>264483.9500000002</v>
+        <v>264684.699999999</v>
       </c>
       <c r="J181">
-        <v>-0.11075441952703502</v>
+        <v>-0.11007945966546719</v>
       </c>
       <c r="K181">
-        <v>-0.10402206895161444</v>
+        <v>-0.11380920548682565</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>0.9893060326576233</v>
       </c>
       <c r="X181">
-        <v>0.9893104367073082</v>
+        <v>0.9893095167900643</v>
       </c>
       <c r="Y181">
         <v>0.9847947955131531</v>
@@ -17234,7 +17234,7 @@
         <v>175.14886624630083</v>
       </c>
       <c r="E182">
-        <v>177.3</v>
+        <v>177.26</v>
       </c>
       <c r="F182">
         <v>175.15</v>
@@ -17243,16 +17243,16 @@
         <v>389524.2740625</v>
       </c>
       <c r="H182">
-        <v>277958.9600000002</v>
+        <v>278093.7099999993</v>
       </c>
       <c r="I182">
-        <v>276081.39999999997</v>
+        <v>277170.6900000001</v>
       </c>
       <c r="J182">
-        <v>-0.2912344149425149</v>
+        <v>-0.2884379525073513</v>
       </c>
       <c r="K182">
-        <v>-0.286414278881626</v>
+        <v>-0.28606834408635956</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>0.993883490562439</v>
       </c>
       <c r="X182">
-        <v>0.9938835822026797</v>
+        <v>0.993882908520785</v>
       </c>
       <c r="Y182">
         <v>0.9924795627593994</v>
@@ -17329,7 +17329,7 @@
         <v>179.70313589810428</v>
       </c>
       <c r="E183">
-        <v>180.5</v>
+        <v>180.35</v>
       </c>
       <c r="F183">
         <v>179.7</v>
@@ -17338,16 +17338,16 @@
         <v>393954.50821875</v>
       </c>
       <c r="H183">
-        <v>287697.9999999998</v>
+        <v>285276.88000000006</v>
       </c>
       <c r="I183">
-        <v>282963.4400000003</v>
+        <v>282806.2999999991</v>
       </c>
       <c r="J183">
-        <v>-0.28173574842585636</v>
+        <v>-0.28213462696823344</v>
       </c>
       <c r="K183">
-        <v>-0.2697177110605609</v>
+        <v>-0.2758633952689909</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>0.9965739548206329</v>
       </c>
       <c r="X183">
-        <v>0.9965739135040346</v>
+        <v>0.9965742458297675</v>
       </c>
       <c r="Y183">
         <v>0.9961040019989014</v>
@@ -17424,7 +17424,7 @@
         <v>186.09129056612096</v>
       </c>
       <c r="E184">
-        <v>187.76</v>
+        <v>187.61</v>
       </c>
       <c r="F184">
         <v>186.23</v>
@@ -17433,16 +17433,16 @@
         <v>414681.57975000003</v>
       </c>
       <c r="H184">
-        <v>302066.7499999991</v>
+        <v>299313.3299999997</v>
       </c>
       <c r="I184">
-        <v>295891.6700000006</v>
+        <v>293704.40000000055</v>
       </c>
       <c r="J184">
-        <v>-0.2864605411738195</v>
+        <v>-0.2917351183598106</v>
       </c>
       <c r="K184">
-        <v>-0.27156940469333907</v>
+        <v>-0.27820924628374527</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>0.9947632849216461</v>
       </c>
       <c r="X184">
-        <v>0.9947655045814864</v>
+        <v>0.9947663296031697</v>
       </c>
       <c r="Y184">
         <v>0.993398904800415</v>
@@ -17519,7 +17519,7 @@
         <v>147.51831388679537</v>
       </c>
       <c r="E185">
-        <v>149.28</v>
+        <v>149.27</v>
       </c>
       <c r="F185">
         <v>147.53</v>
@@ -17528,16 +17528,16 @@
         <v>289105.289671875</v>
       </c>
       <c r="H185">
-        <v>238316.32000000076</v>
+        <v>237257.2999999996</v>
       </c>
       <c r="I185">
-        <v>234085.51</v>
+        <v>233926.23999999982</v>
       </c>
       <c r="J185">
-        <v>-0.19031052574071072</v>
+        <v>-0.1908614322985982</v>
       </c>
       <c r="K185">
-        <v>-0.17567637634551087</v>
+        <v>-0.17933947085755908</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>0.9974283874034882</v>
       </c>
       <c r="X185">
-        <v>0.9974295512048078</v>
+        <v>0.9974282329236893</v>
       </c>
       <c r="Y185">
         <v>0.9959819316864014</v>
@@ -17614,7 +17614,7 @@
         <v>152.28844867323235</v>
       </c>
       <c r="E186">
-        <v>154.84</v>
+        <v>154.83</v>
       </c>
       <c r="F186">
         <v>152.29</v>
@@ -17623,16 +17623,16 @@
         <v>275351.52271875</v>
       </c>
       <c r="H186">
-        <v>260844.69</v>
+        <v>261262.52000000002</v>
       </c>
       <c r="I186">
-        <v>258907.34000000072</v>
+        <v>258980.74000000046</v>
       </c>
       <c r="J186">
-        <v>-0.05972068923528605</v>
+        <v>-0.05945412088921336</v>
       </c>
       <c r="K186">
-        <v>-0.052684773904691964</v>
+        <v>-0.051167331778806946</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>0.9908601343631744</v>
       </c>
       <c r="X186">
-        <v>0.9908591786703866</v>
+        <v>0.990859157859781</v>
       </c>
       <c r="Y186">
         <v>0.9903256893157959</v>
@@ -17709,7 +17709,7 @@
         <v>137.87260044488872</v>
       </c>
       <c r="E187">
-        <v>139.89</v>
+        <v>139.85</v>
       </c>
       <c r="F187">
         <v>137.87</v>
@@ -17718,16 +17718,16 @@
         <v>266760.782484375</v>
       </c>
       <c r="H187">
-        <v>238027.65999999992</v>
+        <v>237367.45999999976</v>
       </c>
       <c r="I187">
-        <v>237250.15000000037</v>
+        <v>237233.1400000002</v>
       </c>
       <c r="J187">
-        <v>-0.11062582816536443</v>
+        <v>-0.11068959316051015</v>
       </c>
       <c r="K187">
-        <v>-0.10771119433966299</v>
+        <v>-0.11018607087080687</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>0.998123049736023</v>
       </c>
       <c r="X187">
-        <v>0.9981122366669224</v>
+        <v>0.9981126073746205</v>
       </c>
       <c r="Y187">
         <v>0.9970951080322266</v>
@@ -17804,7 +17804,7 @@
         <v>172.8108086976314</v>
       </c>
       <c r="E188">
-        <v>173.87</v>
+        <v>173.88</v>
       </c>
       <c r="F188">
         <v>172.81</v>
@@ -17813,16 +17813,16 @@
         <v>387350.42387500004</v>
       </c>
       <c r="H188">
-        <v>300862.3399999998</v>
+        <v>298074.82999999967</v>
       </c>
       <c r="I188">
-        <v>298689.73999999976</v>
+        <v>291941.07999999943</v>
       </c>
       <c r="J188">
-        <v>-0.22889011708842621</v>
+        <v>-0.24631273904527773</v>
       </c>
       <c r="K188">
-        <v>-0.22328124236908126</v>
+        <v>-0.23047759437539705</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>0.996195912361145</v>
       </c>
       <c r="X188">
-        <v>0.9961907879071411</v>
+        <v>0.9961910145298606</v>
       </c>
       <c r="Y188">
         <v>0.9956929087638855</v>
@@ -17908,16 +17908,16 @@
         <v>53627.4064375</v>
       </c>
       <c r="H189">
-        <v>45449.52000000001</v>
+        <v>45651.76</v>
       </c>
       <c r="I189">
-        <v>45245.780000000064</v>
+        <v>45500.98999999987</v>
       </c>
       <c r="J189">
-        <v>-0.15629371238134168</v>
+        <v>-0.15153476510133038</v>
       </c>
       <c r="K189">
-        <v>-0.1524945355511626</v>
+        <v>-0.14872332949375816</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>1336.2589550171244</v>
       </c>
       <c r="E190">
-        <v>1286.96</v>
+        <v>1340.84</v>
       </c>
       <c r="F190">
         <v>1339.73</v>
@@ -17988,16 +17988,16 @@
         <v>2780947.746484375</v>
       </c>
       <c r="H190">
-        <v>2017818.3999999978</v>
+        <v>2297320.750000002</v>
       </c>
       <c r="I190">
-        <v>2294997.8900000043</v>
+        <v>2287521.8700000006</v>
       </c>
       <c r="J190">
-        <v>-0.17474253412301616</v>
+        <v>-0.17743083346609254</v>
       </c>
       <c r="K190">
-        <v>-0.2744134072454658</v>
+        <v>-0.17390725773102567</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>0.6392060816287994</v>
       </c>
       <c r="X190">
-        <v>0.6442759655666601</v>
+        <v>0.6507485227152322</v>
       </c>
       <c r="Y190">
         <v>0.5225970149040222</v>
@@ -18074,7 +18074,7 @@
         <v>316.2027895177017</v>
       </c>
       <c r="E191">
-        <v>316.11</v>
+        <v>316.18</v>
       </c>
       <c r="F191">
         <v>315.33</v>
@@ -18083,16 +18083,16 @@
         <v>686202.976875</v>
       </c>
       <c r="H191">
-        <v>339989.890000001</v>
+        <v>343352.2500000001</v>
       </c>
       <c r="I191">
-        <v>351317.94999999995</v>
+        <v>346074.9899999995</v>
       </c>
       <c r="J191">
-        <v>-0.48802619364911815</v>
+        <v>-0.495666731764935</v>
       </c>
       <c r="K191">
-        <v>-0.5045345160868718</v>
+        <v>-0.4996345664898714</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>312.76672402046444</v>
       </c>
       <c r="E192">
-        <v>312.75</v>
+        <v>312.73</v>
       </c>
       <c r="F192">
         <v>312.73</v>
@@ -18178,16 +18178,16 @@
         <v>638342.849546875</v>
       </c>
       <c r="H192">
-        <v>345789.76999999984</v>
+        <v>332462.1399999981</v>
       </c>
       <c r="I192">
-        <v>327491.6900000008</v>
+        <v>332098.70999999886</v>
       </c>
       <c r="J192">
-        <v>-0.4869658362548129</v>
+        <v>-0.4797486801399315</v>
       </c>
       <c r="K192">
-        <v>-0.4583008641117273</v>
+        <v>-0.47917934659095035</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>0.9988773465156555</v>
       </c>
       <c r="X192">
-        <v>0.9988773465156555</v>
+        <v>0.9988773465156554</v>
       </c>
       <c r="Y192">
         <v>0.9988773465156555</v>
@@ -18273,16 +18273,16 @@
         <v>560095.204953125</v>
       </c>
       <c r="H193">
-        <v>501068.1799999984</v>
+        <v>480161.609999999</v>
       </c>
       <c r="I193">
-        <v>500375.97</v>
+        <v>480715.8199999999</v>
       </c>
       <c r="J193">
-        <v>-0.10662336407276149</v>
+        <v>-0.14172480723124284</v>
       </c>
       <c r="K193">
-        <v>-0.10538748489744096</v>
+        <v>-0.1427142997230546</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -18576,13 +18576,13 @@
         <v>220.03</v>
       </c>
       <c r="D2">
-        <v>282597.8600000013</v>
+        <v>284640.8199999999</v>
       </c>
       <c r="E2">
         <v>220.03</v>
       </c>
       <c r="F2">
-        <v>282967.79999999894</v>
+        <v>285379.4500000004</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -18616,13 +18616,13 @@
         <v>359.67</v>
       </c>
       <c r="D3">
-        <v>595276.4799999967</v>
+        <v>596919.6400000033</v>
       </c>
       <c r="E3">
         <v>359.67</v>
       </c>
       <c r="F3">
-        <v>594833.2799999993</v>
+        <v>597096.9700000016</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -18653,16 +18653,16 @@
         </is>
       </c>
       <c r="C4">
-        <v>248.77</v>
+        <v>248.83</v>
       </c>
       <c r="D4">
-        <v>397624.0799999984</v>
+        <v>396152.8899999994</v>
       </c>
       <c r="E4">
         <v>236.73</v>
       </c>
       <c r="F4">
-        <v>376862.5700000005</v>
+        <v>382861.289999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>0.7397138476371765</v>
       </c>
       <c r="O4">
-        <v>0.7540504954068132</v>
+        <v>0.7539801432518644</v>
       </c>
       <c r="P4">
         <v>0.5311591029167175</v>
@@ -18711,13 +18711,13 @@
         <v>12.16</v>
       </c>
       <c r="D5">
-        <v>12449.260000000022</v>
+        <v>12953.610000000011</v>
       </c>
       <c r="E5">
         <v>12.16</v>
       </c>
       <c r="F5">
-        <v>12581.510000000011</v>
+        <v>13057.290000000025</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -18751,13 +18751,13 @@
         <v>0.04</v>
       </c>
       <c r="D6">
-        <v>48.060000000000436</v>
+        <v>46.38000000000032</v>
       </c>
       <c r="E6">
         <v>0.04</v>
       </c>
       <c r="F6">
-        <v>48.57000000000032</v>
+        <v>46.23000000000035</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -18791,13 +18791,13 @@
         <v>5711.94</v>
       </c>
       <c r="D7">
-        <v>9902020.160000049</v>
+        <v>9901393.940000026</v>
       </c>
       <c r="E7">
         <v>5711.94</v>
       </c>
       <c r="F7">
-        <v>9899855.049999975</v>
+        <v>9900546.830000013</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -18831,13 +18831,13 @@
         <v>309.48</v>
       </c>
       <c r="D8">
-        <v>375554.69999999925</v>
+        <v>377792.8800000007</v>
       </c>
       <c r="E8">
         <v>309.48</v>
       </c>
       <c r="F8">
-        <v>376545.78999999963</v>
+        <v>381246.6900000008</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -18871,13 +18871,13 @@
         <v>566.15</v>
       </c>
       <c r="D9">
-        <v>862415.0599999992</v>
+        <v>862912.55</v>
       </c>
       <c r="E9">
         <v>566.15</v>
       </c>
       <c r="F9">
-        <v>862287.1100000018</v>
+        <v>863970.7400000035</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -18911,13 +18911,13 @@
         <v>187.95</v>
       </c>
       <c r="D10">
-        <v>322933.56999999983</v>
+        <v>319381.35999999935</v>
       </c>
       <c r="E10">
         <v>187.95</v>
       </c>
       <c r="F10">
-        <v>325428.59999999864</v>
+        <v>325741.52999999974</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -18948,16 +18948,16 @@
         </is>
       </c>
       <c r="C11">
-        <v>256.47</v>
+        <v>256.58</v>
       </c>
       <c r="D11">
-        <v>434579.65999999875</v>
+        <v>434717.34999999916</v>
       </c>
       <c r="E11">
         <v>252.63</v>
       </c>
       <c r="F11">
-        <v>432354.65999999957</v>
+        <v>432126.65999999864</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>0.9934870600700378</v>
       </c>
       <c r="O11">
-        <v>0.9934611781953648</v>
+        <v>0.9934603274538051</v>
       </c>
       <c r="P11">
         <v>0.9897304773330688</v>
@@ -19003,16 +19003,16 @@
         </is>
       </c>
       <c r="C12">
-        <v>219.08</v>
+        <v>219.11</v>
       </c>
       <c r="D12">
-        <v>372471.9499999999</v>
+        <v>371538.65999999957</v>
       </c>
       <c r="E12">
         <v>200.96</v>
       </c>
       <c r="F12">
-        <v>348365.6599999999</v>
+        <v>348058.9400000003</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>0.9973084330558777</v>
       </c>
       <c r="O12">
-        <v>0.9973085047402973</v>
+        <v>0.9973084397345828</v>
       </c>
       <c r="P12">
         <v>0.9969450831413269</v>
@@ -19061,13 +19061,13 @@
         <v>241.68</v>
       </c>
       <c r="D13">
-        <v>415966.35000000027</v>
+        <v>415359.34000000043</v>
       </c>
       <c r="E13">
         <v>241.68</v>
       </c>
       <c r="F13">
-        <v>416099.3600000001</v>
+        <v>414964.88999999966</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -19101,13 +19101,13 @@
         <v>233.98</v>
       </c>
       <c r="D14">
-        <v>405547.5200000004</v>
+        <v>405158.4500000009</v>
       </c>
       <c r="E14">
         <v>233.98</v>
       </c>
       <c r="F14">
-        <v>405491.13000000064</v>
+        <v>405651.87999999913</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -19141,13 +19141,13 @@
         <v>6865.57</v>
       </c>
       <c r="D15">
-        <v>11917906.53000001</v>
+        <v>11917650.250000026</v>
       </c>
       <c r="E15">
         <v>6865.57</v>
       </c>
       <c r="F15">
-        <v>11920845.899999967</v>
+        <v>11918912.789999997</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -19181,13 +19181,13 @@
         <v>1771.22</v>
       </c>
       <c r="D16">
-        <v>3052674.660000012</v>
+        <v>3050362.6499999897</v>
       </c>
       <c r="E16">
         <v>1771.22</v>
       </c>
       <c r="F16">
-        <v>3052716.1199999973</v>
+        <v>3052143.1800000113</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -19218,16 +19218,16 @@
         </is>
       </c>
       <c r="C17">
-        <v>674.81</v>
+        <v>671.42</v>
       </c>
       <c r="D17">
-        <v>972269.1100000024</v>
+        <v>981901.8000000023</v>
       </c>
       <c r="E17">
         <v>686.89</v>
       </c>
       <c r="F17">
-        <v>970762.689999999</v>
+        <v>998971.2799999991</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>0.9982466697692871</v>
       </c>
       <c r="O17">
-        <v>0.9982466697692871</v>
+        <v>0.9982466697692872</v>
       </c>
       <c r="P17">
         <v>0.9982466697692871</v>
@@ -19276,13 +19276,13 @@
         <v>600.35</v>
       </c>
       <c r="D18">
-        <v>959285.3499999981</v>
+        <v>961514.0099999994</v>
       </c>
       <c r="E18">
         <v>600.35</v>
       </c>
       <c r="F18">
-        <v>963744.2000000022</v>
+        <v>965908.08</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -19313,16 +19313,16 @@
         </is>
       </c>
       <c r="C19">
-        <v>381.67</v>
+        <v>381.56</v>
       </c>
       <c r="D19">
-        <v>649715.0399999985</v>
+        <v>649201.8500000001</v>
       </c>
       <c r="E19">
         <v>374.42</v>
       </c>
       <c r="F19">
-        <v>649220.1499999969</v>
+        <v>648926.7199999993</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -19371,13 +19371,13 @@
         <v>3449.19</v>
       </c>
       <c r="D20">
-        <v>5703630.060000023</v>
+        <v>5743025.799999985</v>
       </c>
       <c r="E20">
         <v>3449.19</v>
       </c>
       <c r="F20">
-        <v>5715743.749999993</v>
+        <v>5764702.830000007</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -19408,16 +19408,16 @@
         </is>
       </c>
       <c r="C21">
-        <v>424.26</v>
+        <v>398.28</v>
       </c>
       <c r="D21">
-        <v>739143.3100000012</v>
+        <v>691394.2399999999</v>
       </c>
       <c r="E21">
         <v>401.04</v>
       </c>
       <c r="F21">
-        <v>655782.1000000023</v>
+        <v>670961.2199999989</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>0.6392060816287994</v>
       </c>
       <c r="O21">
-        <v>0.5864406048176476</v>
+        <v>0.5840415111010421</v>
       </c>
       <c r="P21">
         <v>0.5225970149040222</v>
@@ -19463,16 +19463,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>1010.78</v>
+        <v>827.61</v>
       </c>
       <c r="D22">
-        <v>1681150.9899999967</v>
+        <v>1363363.5799999963</v>
       </c>
       <c r="E22">
         <v>823.74</v>
       </c>
       <c r="F22">
-        <v>1300525.219999997</v>
+        <v>1362668.2000000011</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>0.9648301005363464</v>
       </c>
       <c r="O22">
-        <v>0.9660290926991985</v>
+        <v>0.9656488080651502</v>
       </c>
       <c r="P22">
         <v>0.9619141221046448</v>
@@ -19518,16 +19518,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>619.85</v>
+        <v>616.49</v>
       </c>
       <c r="D23">
-        <v>1051130.0500000003</v>
+        <v>1043934.5099999971</v>
       </c>
       <c r="E23">
         <v>574.05</v>
       </c>
       <c r="F23">
-        <v>970510.4400000013</v>
+        <v>977324.7700000005</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>0.9609273374080658</v>
       </c>
       <c r="O23">
-        <v>0.961016051417217</v>
+        <v>0.9610236605031198</v>
       </c>
       <c r="P23">
         <v>0.9594816565513611</v>
@@ -19573,16 +19573,16 @@
         </is>
       </c>
       <c r="C24">
-        <v>325.75</v>
+        <v>325.66</v>
       </c>
       <c r="D24">
-        <v>521420.90000000014</v>
+        <v>521278.15999999916</v>
       </c>
       <c r="E24">
         <v>311.07</v>
       </c>
       <c r="F24">
-        <v>499287.8499999981</v>
+        <v>494594.6200000007</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -19628,16 +19628,16 @@
         </is>
       </c>
       <c r="C25">
-        <v>40.78</v>
+        <v>40.81</v>
       </c>
       <c r="D25">
-        <v>69076.99000000015</v>
+        <v>67901.10000000031</v>
       </c>
       <c r="E25">
         <v>39.72</v>
       </c>
       <c r="F25">
-        <v>65383.29000000012</v>
+        <v>63051.030000000064</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -19686,13 +19686,13 @@
         <v>428.06</v>
       </c>
       <c r="D26">
-        <v>741990.959999998</v>
+        <v>741900.2199999987</v>
       </c>
       <c r="E26">
         <v>428.06</v>
       </c>
       <c r="F26">
-        <v>742422.9699999986</v>
+        <v>741685.1599999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -19726,13 +19726,13 @@
         <v>196.28</v>
       </c>
       <c r="D27">
-        <v>324536.1199999997</v>
+        <v>324940.78000000014</v>
       </c>
       <c r="E27">
         <v>196.28</v>
       </c>
       <c r="F27">
-        <v>324743.5899999996</v>
+        <v>324080.1700000011</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -19766,13 +19766,13 @@
         <v>66.75</v>
       </c>
       <c r="D28">
-        <v>108955.02999999994</v>
+        <v>115760.96000000024</v>
       </c>
       <c r="E28">
         <v>66.75</v>
       </c>
       <c r="F28">
-        <v>109269.22000000022</v>
+        <v>115430.74</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -19806,13 +19806,13 @@
         <v>298.15</v>
       </c>
       <c r="D29">
-        <v>511755.18000000075</v>
+        <v>511225.59000000067</v>
       </c>
       <c r="E29">
         <v>298.15</v>
       </c>
       <c r="F29">
-        <v>511400.01</v>
+        <v>510407.8899999991</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -19843,16 +19843,16 @@
         </is>
       </c>
       <c r="C30">
-        <v>229.18</v>
+        <v>229.12</v>
       </c>
       <c r="D30">
-        <v>384813.5800000008</v>
+        <v>383898.81999999937</v>
       </c>
       <c r="E30">
         <v>228.0</v>
       </c>
       <c r="F30">
-        <v>384093.6600000009</v>
+        <v>383436.63000000064</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>0.987289309501648</v>
       </c>
       <c r="O30">
-        <v>0.9872885995355051</v>
+        <v>0.9872912583767713</v>
       </c>
       <c r="P30">
         <v>0.982359766960144</v>
@@ -19898,16 +19898,16 @@
         </is>
       </c>
       <c r="C31">
-        <v>196.36</v>
+        <v>196.35</v>
       </c>
       <c r="D31">
-        <v>301648.30999999976</v>
+        <v>299192.1899999997</v>
       </c>
       <c r="E31">
         <v>194.36</v>
       </c>
       <c r="F31">
-        <v>301011.6500000005</v>
+        <v>298326.8700000001</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>0.995455801486969</v>
       </c>
       <c r="O31">
-        <v>0.9954569733455968</v>
+        <v>0.9954568220149478</v>
       </c>
       <c r="P31">
         <v>0.994864284992218</v>
@@ -19956,13 +19956,13 @@
         <v>224.42</v>
       </c>
       <c r="D32">
-        <v>357452.84999999875</v>
+        <v>359207.59999999974</v>
       </c>
       <c r="E32">
         <v>224.42</v>
       </c>
       <c r="F32">
-        <v>363268.59999999905</v>
+        <v>360946.86999999924</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -19993,16 +19993,16 @@
         </is>
       </c>
       <c r="C33">
-        <v>142.77</v>
+        <v>142.78</v>
       </c>
       <c r="D33">
-        <v>245023.74000000014</v>
+        <v>245326.8400000003</v>
       </c>
       <c r="E33">
         <v>141.79</v>
       </c>
       <c r="F33">
-        <v>244785.9200000003</v>
+        <v>245012.48000000016</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>0.9941704273223877</v>
       </c>
       <c r="O33">
-        <v>0.9941669007395678</v>
+        <v>0.9941641066948423</v>
       </c>
       <c r="P33">
         <v>0.9901884198188782</v>
@@ -20048,16 +20048,16 @@
         </is>
       </c>
       <c r="C34">
-        <v>147.8</v>
+        <v>147.86</v>
       </c>
       <c r="D34">
-        <v>248708.55999999956</v>
+        <v>249186.60999999978</v>
       </c>
       <c r="E34">
         <v>145.93</v>
       </c>
       <c r="F34">
-        <v>250703.2699999997</v>
+        <v>250365.17000000045</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>0.9998248517513275</v>
       </c>
       <c r="O34">
-        <v>0.9998253836429636</v>
+        <v>0.9998253362468537</v>
       </c>
       <c r="P34">
         <v>0.9997138381004333</v>
@@ -20106,13 +20106,13 @@
         <v>495.25</v>
       </c>
       <c r="D35">
-        <v>810283.7999999975</v>
+        <v>812088.0699999996</v>
       </c>
       <c r="E35">
         <v>495.25</v>
       </c>
       <c r="F35">
-        <v>811339.7200000001</v>
+        <v>811807.5099999992</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -20143,16 +20143,16 @@
         </is>
       </c>
       <c r="C36">
-        <v>304.94</v>
+        <v>305.15</v>
       </c>
       <c r="D36">
-        <v>471358.70000000024</v>
+        <v>474458.9999999987</v>
       </c>
       <c r="E36">
         <v>301.57</v>
       </c>
       <c r="F36">
-        <v>468131.05000000057</v>
+        <v>472181.7400000001</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>0.9990717470645905</v>
       </c>
       <c r="O36">
-        <v>0.9990712628117275</v>
+        <v>0.9990712566867771</v>
       </c>
       <c r="P36">
         <v>0.9990215301513672</v>
@@ -20198,16 +20198,16 @@
         </is>
       </c>
       <c r="C37">
-        <v>260.72</v>
+        <v>260.6</v>
       </c>
       <c r="D37">
-        <v>390861.09999999875</v>
+        <v>390549.13000000024</v>
       </c>
       <c r="E37">
         <v>256.6</v>
       </c>
       <c r="F37">
-        <v>390049.6800000012</v>
+        <v>388059.759999999</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>0.9990639686584473</v>
       </c>
       <c r="O37">
-        <v>0.9990620791681777</v>
+        <v>0.999062122332558</v>
       </c>
       <c r="P37">
         <v>0.9988018274307251</v>
@@ -20253,16 +20253,16 @@
         </is>
       </c>
       <c r="C38">
-        <v>234.41</v>
+        <v>234.39</v>
       </c>
       <c r="D38">
-        <v>334770.58999999875</v>
+        <v>335600.44000000134</v>
       </c>
       <c r="E38">
         <v>229.89</v>
       </c>
       <c r="F38">
-        <v>332280.5800000003</v>
+        <v>335994.04000000004</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>0.9948042929172516</v>
       </c>
       <c r="O38">
-        <v>0.9948189874580664</v>
+        <v>0.9948194023474046</v>
       </c>
       <c r="P38">
         <v>0.9902637004852295</v>
@@ -20308,16 +20308,16 @@
         </is>
       </c>
       <c r="C39">
-        <v>247.71</v>
+        <v>247.65</v>
       </c>
       <c r="D39">
-        <v>349323.82000000076</v>
+        <v>350533.11999999895</v>
       </c>
       <c r="E39">
         <v>244.36</v>
       </c>
       <c r="F39">
-        <v>345860.31</v>
+        <v>349325.70999999944</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>0.9978305697441101</v>
       </c>
       <c r="O39">
-        <v>0.9978317786005905</v>
+        <v>0.9978310834867776</v>
       </c>
       <c r="P39">
         <v>0.996639609336853</v>
@@ -20366,13 +20366,13 @@
         <v>31.39</v>
       </c>
       <c r="D40">
-        <v>52747.56999999984</v>
+        <v>52495.180000000095</v>
       </c>
       <c r="E40">
         <v>31.39</v>
       </c>
       <c r="F40">
-        <v>52684.760000000024</v>
+        <v>52661.28000000009</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -20403,16 +20403,16 @@
         </is>
       </c>
       <c r="C41">
-        <v>185.21</v>
+        <v>185.16</v>
       </c>
       <c r="D41">
-        <v>294348.5800000003</v>
+        <v>295086.61000000034</v>
       </c>
       <c r="E41">
         <v>182.37</v>
       </c>
       <c r="F41">
-        <v>293730.8099999996</v>
+        <v>295229.7299999991</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>0.9896457493305206</v>
       </c>
       <c r="O41">
-        <v>0.9897013708354849</v>
+        <v>0.9897000738386865</v>
       </c>
       <c r="P41">
         <v>0.9815158843994141</v>
@@ -20461,13 +20461,13 @@
         <v>183.4</v>
       </c>
       <c r="D42">
-        <v>297659.90999999933</v>
+        <v>297255.8099999989</v>
       </c>
       <c r="E42">
         <v>178.03</v>
       </c>
       <c r="F42">
-        <v>291377.77000000014</v>
+        <v>293707.1199999997</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>0.9890185594558716</v>
       </c>
       <c r="O42">
-        <v>0.9890581796628573</v>
+        <v>0.9890569847759477</v>
       </c>
       <c r="P42">
         <v>0.9854037165641785</v>
@@ -20516,13 +20516,13 @@
         <v>177.11</v>
       </c>
       <c r="D43">
-        <v>302452.3899999988</v>
+        <v>303035.9000000003</v>
       </c>
       <c r="E43">
         <v>177.11</v>
       </c>
       <c r="F43">
-        <v>302643.2700000008</v>
+        <v>303283.4299999998</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -20556,13 +20556,13 @@
         <v>127.47</v>
       </c>
       <c r="D44">
-        <v>220962.19999999998</v>
+        <v>218333.07000000004</v>
       </c>
       <c r="E44">
         <v>127.47</v>
       </c>
       <c r="F44">
-        <v>220709.28000000003</v>
+        <v>218846.08999999912</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -20596,13 +20596,13 @@
         <v>138.94</v>
       </c>
       <c r="D45">
-        <v>240775.06999999992</v>
+        <v>240113.02999999977</v>
       </c>
       <c r="E45">
         <v>138.94</v>
       </c>
       <c r="F45">
-        <v>240786.5900000002</v>
+        <v>239625.31000000046</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -20636,13 +20636,13 @@
         <v>172.9</v>
       </c>
       <c r="D46">
-        <v>299279.19999999943</v>
+        <v>299345.35999999987</v>
       </c>
       <c r="E46">
         <v>172.9</v>
       </c>
       <c r="F46">
-        <v>299225.979999999</v>
+        <v>299219.2999999996</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -20676,13 +20676,13 @@
         <v>143.48</v>
       </c>
       <c r="D47">
-        <v>248708.93000000055</v>
+        <v>248268.2699999998</v>
       </c>
       <c r="E47">
         <v>143.48</v>
       </c>
       <c r="F47">
-        <v>248283.78000000064</v>
+        <v>248526.90000000029</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -20713,16 +20713,16 @@
         </is>
       </c>
       <c r="C48">
-        <v>270.74</v>
+        <v>269.68</v>
       </c>
       <c r="D48">
-        <v>279817.74</v>
+        <v>258096.76999999958</v>
       </c>
       <c r="E48">
         <v>262.29</v>
       </c>
       <c r="F48">
-        <v>266126.42000000033</v>
+        <v>267658.00000000076</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>0.7220398783683777</v>
       </c>
       <c r="O48">
-        <v>0.6716117159811339</v>
+        <v>0.6698752912762768</v>
       </c>
       <c r="P48">
         <v>0.5120963454246521</v>
@@ -20771,13 +20771,13 @@
         <v>258.96</v>
       </c>
       <c r="D49">
-        <v>367782.2999999997</v>
+        <v>352304.3800000007</v>
       </c>
       <c r="E49">
         <v>258.96</v>
       </c>
       <c r="F49">
-        <v>375877.0199999999</v>
+        <v>368687.3799999993</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -20811,13 +20811,13 @@
         <v>3.76</v>
       </c>
       <c r="D50">
-        <v>6519.999999999991</v>
+        <v>6524.820000000006</v>
       </c>
       <c r="E50">
         <v>3.76</v>
       </c>
       <c r="F50">
-        <v>6522.769999999999</v>
+        <v>6523.969999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -20851,13 +20851,13 @@
         <v>3.78</v>
       </c>
       <c r="D51">
-        <v>6551.389999999999</v>
+        <v>6552.870000000002</v>
       </c>
       <c r="E51">
         <v>3.78</v>
       </c>
       <c r="F51">
-        <v>6550.840000000006</v>
+        <v>6543.479999999985</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -20891,13 +20891,13 @@
         <v>3.76</v>
       </c>
       <c r="D52">
-        <v>6526.060000000007</v>
+        <v>6516.2199999999975</v>
       </c>
       <c r="E52">
         <v>3.76</v>
       </c>
       <c r="F52">
-        <v>6526.390000000012</v>
+        <v>6515.960000000002</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
